--- a/plantillas/PLANTILLA_CLIENTE.xlsx
+++ b/plantillas/PLANTILLA_CLIENTE.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="55">
   <si>
     <t xml:space="preserve">Cómo se rellena esta plantilla</t>
   </si>
@@ -64,28 +64,34 @@
     <t xml:space="preserve">4. Sesión: nombre de la sesión (Pierna, Tracc, Empuje…). Opcional; si se deja vacío será «Entreno lunes».</t>
   </si>
   <si>
-    <t xml:space="preserve">5. Bloque: Activación / P. Principal / Accesorios / Vuelta a la calma. Se pone al empezar cada bloque; las filas de debajo heredan.</t>
+    <t xml:space="preserve">5. Bloque: Activación / P. Principal / Aeróbico / Accesorios / Vuelta a la calma. Se pone al empezar cada bloque; las filas de debajo heredan.</t>
   </si>
   <si>
-    <t xml:space="preserve">6. A la app solo pasa el bloque «P. Principal». Lo demás se queda en el Excel.</t>
+    <t xml:space="preserve">6. A la app pasan la Activación (como lista para marcar, sin carga), la P. Principal y el Aeróbico. Accesorios y Vuelta a la calma se quedan en el Excel.</t>
   </si>
   <si>
-    <t xml:space="preserve">7. Series y Reps: solo números. Lo que no sea número (6-8, EA, por lado, 3x4") va en «Nota reps».</t>
+    <t xml:space="preserve">7. Aeróbico (al final de la sesión): Bloque «Aeróbico», Ejercicio = Carrera, Bicicleta…, y Minutos + Zona o Intervalos («10 Z2, 3 Z4, 10 Z2»). Una fila por sesión. Se graba con el pulsómetro dentro de la misma sesión.</t>
   </si>
   <si>
-    <t xml:space="preserve">8. Biseries: dos filas seguidas (una por ejercicio) o «Ejercicio A + Ejercicio B» en una fila.</t>
+    <t xml:space="preserve">8. RPE pre y RPE post: para anotar lo que os diga el cliente, en la primera fila de cada día. No pasan a la app (allí lo anota el cliente).</t>
   </si>
   <si>
-    <t xml:space="preserve">9. Unilateral / Pliometría: elige «Sí» si lo es. En pliometría, Reps = contactos.</t>
+    <t xml:space="preserve">9. Series y Reps: solo números. Lo que no sea número (6-8, EA, por lado, 3x4") va en «Nota reps».</t>
   </si>
   <si>
-    <t xml:space="preserve">10. Peso (kg): solo el número (17,5). Si hace falta texto («por lado», «poner lastre»), va en Observaciones.</t>
+    <t xml:space="preserve">10. Biseries: dos filas seguidas (una por ejercicio) o «Ejercicio A + Ejercicio B» en una fila.</t>
   </si>
   <si>
-    <t xml:space="preserve">11. No cambies los títulos de la fila 4 ni la celda «SEMANA DEL». Puedes añadir más pestañas (ANUAL, RM…): se ignoran.</t>
+    <t xml:space="preserve">11. Unilateral / Pliometría: elige «Sí» si lo es. En pliometría, Reps = contactos.</t>
   </si>
   <si>
-    <t xml:space="preserve">12. Para el mes siguiente: Archivo &gt; Guardar una copia, cambia la fecha amarilla y borra las filas.</t>
+    <t xml:space="preserve">12. Peso (kg): solo el número (17,5). Si hace falta texto («por lado», «poner lastre»), va en Observaciones.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13. No cambies los títulos de la fila 4 ni la celda «SEMANA DEL». Puedes añadir más pestañas (ANUAL, RM…): se ignoran.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14. Para el mes siguiente: Archivo &gt; Guardar una copia, cambia la fecha amarilla y borra las filas.</t>
   </si>
   <si>
     <t xml:space="preserve">Ejemplo (esta pestaña no se importa):</t>
@@ -124,7 +130,22 @@
     <t xml:space="preserve">Pliometría</t>
   </si>
   <si>
+    <t xml:space="preserve">Minutos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intervalos</t>
+  </si>
+  <si>
     <t xml:space="preserve">Observaciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPE pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPE post</t>
   </si>
   <si>
     <t xml:space="preserve">Lunes</t>
@@ -160,6 +181,15 @@
     <t xml:space="preserve">Drop jump</t>
   </si>
   <si>
+    <t xml:space="preserve">Aeróbico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bicicleta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jueves</t>
   </si>
   <si>
@@ -170,6 +200,12 @@
   </si>
   <si>
     <t xml:space="preserve">Descanso 2 min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 Z2, 4x(2 Z4, 1 Z1)</t>
   </si>
   <si>
     <t xml:space="preserve">SEMANA DEL</t>
@@ -661,7 +697,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
@@ -673,7 +709,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="0" width="8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -696,6 +736,11 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
@@ -712,6 +757,11 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
@@ -728,6 +778,11 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
@@ -744,6 +799,11 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
@@ -760,6 +820,11 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
@@ -776,6 +841,11 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
@@ -792,6 +862,11 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
@@ -808,6 +883,11 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
@@ -824,6 +904,11 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
@@ -840,6 +925,11 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
@@ -856,6 +946,11 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
@@ -872,164 +967,186 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="4" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="B19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="C19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="D19" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="E19" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="F19" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="H19" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="I19" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L17" s="4" t="s">
+      <c r="J19" s="4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
+      <c r="K19" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="L19" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="M19" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="N19" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="O19" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="P19" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q19" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F20" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>10</v>
-      </c>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
       <c r="I20" s="5"/>
-      <c r="J20" s="5" t="s">
-        <v>35</v>
-      </c>
+      <c r="J20" s="5"/>
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
+      <c r="C21" s="5" t="s">
+        <v>37</v>
+      </c>
       <c r="D21" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
+        <v>8</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>7</v>
+      </c>
       <c r="J21" s="5"/>
-      <c r="K21" s="5" t="s">
-        <v>35</v>
-      </c>
+      <c r="K21" s="5"/>
       <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>30</v>
-      </c>
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
       <c r="D22" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>3</v>
@@ -1037,33 +1154,160 @@
       <c r="F22" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="G22" s="5"/>
+      <c r="G22" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="H22" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="I22" s="5" t="n">
+      <c r="I25" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="P25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q25" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="A9:L9"/>
-    <mergeCell ref="A10:L10"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A12:L12"/>
-    <mergeCell ref="A13:L13"/>
-    <mergeCell ref="A14:L14"/>
+  <mergeCells count="14">
+    <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A5:Q5"/>
+    <mergeCell ref="A6:Q6"/>
+    <mergeCell ref="A7:Q7"/>
+    <mergeCell ref="A8:Q8"/>
+    <mergeCell ref="A9:Q9"/>
+    <mergeCell ref="A10:Q10"/>
+    <mergeCell ref="A11:Q11"/>
+    <mergeCell ref="A12:Q12"/>
+    <mergeCell ref="A13:Q13"/>
+    <mergeCell ref="A14:Q14"/>
+    <mergeCell ref="A15:Q15"/>
+    <mergeCell ref="A16:Q16"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1080,7 +1324,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:Q84"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
@@ -1092,12 +1336,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="0" width="8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B1" s="7" t="n">
         <v>46328</v>
@@ -1109,46 +1357,61 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B2" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1163,7 +1426,12 @@
       <c r="I5" s="10"/>
       <c r="J5" s="10"/>
       <c r="K5" s="10"/>
-      <c r="L5" s="5"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
@@ -1177,7 +1445,12 @@
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
-      <c r="L6" s="5"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
@@ -1191,7 +1464,12 @@
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
-      <c r="L7" s="5"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
@@ -1205,7 +1483,12 @@
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
-      <c r="L8" s="5"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
@@ -1219,7 +1502,12 @@
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
-      <c r="L9" s="5"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
@@ -1233,7 +1521,12 @@
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
-      <c r="L10" s="5"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
@@ -1247,7 +1540,12 @@
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
-      <c r="L11" s="5"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
@@ -1261,7 +1559,12 @@
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
-      <c r="L12" s="5"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
@@ -1275,7 +1578,12 @@
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
-      <c r="L13" s="5"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
@@ -1289,7 +1597,12 @@
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
-      <c r="L14" s="5"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
@@ -1303,7 +1616,12 @@
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
-      <c r="L15" s="5"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5"/>
@@ -1317,7 +1635,12 @@
       <c r="I16" s="10"/>
       <c r="J16" s="10"/>
       <c r="K16" s="10"/>
-      <c r="L16" s="5"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5"/>
@@ -1331,7 +1654,12 @@
       <c r="I17" s="10"/>
       <c r="J17" s="10"/>
       <c r="K17" s="10"/>
-      <c r="L17" s="5"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5"/>
@@ -1345,7 +1673,12 @@
       <c r="I18" s="10"/>
       <c r="J18" s="10"/>
       <c r="K18" s="10"/>
-      <c r="L18" s="5"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5"/>
@@ -1359,7 +1692,12 @@
       <c r="I19" s="10"/>
       <c r="J19" s="10"/>
       <c r="K19" s="10"/>
-      <c r="L19" s="5"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5"/>
@@ -1373,7 +1711,12 @@
       <c r="I20" s="10"/>
       <c r="J20" s="10"/>
       <c r="K20" s="10"/>
-      <c r="L20" s="5"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5"/>
@@ -1387,7 +1730,12 @@
       <c r="I21" s="10"/>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
-      <c r="L21" s="5"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5"/>
@@ -1401,7 +1749,12 @@
       <c r="I22" s="10"/>
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
-      <c r="L22" s="5"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5"/>
@@ -1415,7 +1768,12 @@
       <c r="I23" s="10"/>
       <c r="J23" s="10"/>
       <c r="K23" s="10"/>
-      <c r="L23" s="5"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5"/>
@@ -1429,7 +1787,12 @@
       <c r="I24" s="10"/>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
-      <c r="L24" s="5"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5"/>
@@ -1443,7 +1806,12 @@
       <c r="I25" s="10"/>
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
-      <c r="L25" s="5"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5"/>
@@ -1457,7 +1825,12 @@
       <c r="I26" s="10"/>
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
-      <c r="L26" s="5"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5"/>
@@ -1471,7 +1844,12 @@
       <c r="I27" s="10"/>
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
-      <c r="L27" s="5"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5"/>
@@ -1485,7 +1863,12 @@
       <c r="I28" s="10"/>
       <c r="J28" s="10"/>
       <c r="K28" s="10"/>
-      <c r="L28" s="5"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5"/>
@@ -1499,7 +1882,12 @@
       <c r="I29" s="10"/>
       <c r="J29" s="10"/>
       <c r="K29" s="10"/>
-      <c r="L29" s="5"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5"/>
@@ -1513,7 +1901,12 @@
       <c r="I30" s="10"/>
       <c r="J30" s="10"/>
       <c r="K30" s="10"/>
-      <c r="L30" s="5"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="10"/>
+      <c r="Q30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5"/>
@@ -1527,7 +1920,12 @@
       <c r="I31" s="10"/>
       <c r="J31" s="10"/>
       <c r="K31" s="10"/>
-      <c r="L31" s="5"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="10"/>
+      <c r="Q31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5"/>
@@ -1541,7 +1939,12 @@
       <c r="I32" s="10"/>
       <c r="J32" s="10"/>
       <c r="K32" s="10"/>
-      <c r="L32" s="5"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="10"/>
+      <c r="Q32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5"/>
@@ -1555,7 +1958,12 @@
       <c r="I33" s="10"/>
       <c r="J33" s="10"/>
       <c r="K33" s="10"/>
-      <c r="L33" s="5"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="10"/>
+      <c r="Q33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5"/>
@@ -1569,7 +1977,12 @@
       <c r="I34" s="10"/>
       <c r="J34" s="10"/>
       <c r="K34" s="10"/>
-      <c r="L34" s="5"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5"/>
@@ -1583,7 +1996,12 @@
       <c r="I35" s="10"/>
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
-      <c r="L35" s="5"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5"/>
@@ -1597,7 +2015,12 @@
       <c r="I36" s="10"/>
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
-      <c r="L36" s="5"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="10"/>
+      <c r="Q36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5"/>
@@ -1611,7 +2034,12 @@
       <c r="I37" s="10"/>
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
-      <c r="L37" s="5"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5"/>
@@ -1625,7 +2053,12 @@
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
-      <c r="L38" s="5"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5"/>
@@ -1639,7 +2072,12 @@
       <c r="I39" s="10"/>
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
-      <c r="L39" s="5"/>
+      <c r="L39" s="10"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5"/>
@@ -1653,7 +2091,12 @@
       <c r="I40" s="10"/>
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
-      <c r="L40" s="5"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="10"/>
+      <c r="Q40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5"/>
@@ -1667,7 +2110,12 @@
       <c r="I41" s="10"/>
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
-      <c r="L41" s="5"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5"/>
@@ -1681,7 +2129,12 @@
       <c r="I42" s="10"/>
       <c r="J42" s="10"/>
       <c r="K42" s="10"/>
-      <c r="L42" s="5"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="10"/>
+      <c r="Q42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5"/>
@@ -1695,7 +2148,12 @@
       <c r="I43" s="10"/>
       <c r="J43" s="10"/>
       <c r="K43" s="10"/>
-      <c r="L43" s="5"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="10"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5"/>
@@ -1709,7 +2167,12 @@
       <c r="I44" s="10"/>
       <c r="J44" s="10"/>
       <c r="K44" s="10"/>
-      <c r="L44" s="5"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="10"/>
+      <c r="Q44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5"/>
@@ -1723,7 +2186,12 @@
       <c r="I45" s="10"/>
       <c r="J45" s="10"/>
       <c r="K45" s="10"/>
-      <c r="L45" s="5"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="10"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5"/>
@@ -1737,7 +2205,12 @@
       <c r="I46" s="10"/>
       <c r="J46" s="10"/>
       <c r="K46" s="10"/>
-      <c r="L46" s="5"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="10"/>
+      <c r="Q46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5"/>
@@ -1751,7 +2224,12 @@
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
       <c r="K47" s="10"/>
-      <c r="L47" s="5"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="10"/>
+      <c r="Q47" s="10"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5"/>
@@ -1765,7 +2243,12 @@
       <c r="I48" s="10"/>
       <c r="J48" s="10"/>
       <c r="K48" s="10"/>
-      <c r="L48" s="5"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="10"/>
+      <c r="Q48" s="10"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5"/>
@@ -1779,7 +2262,12 @@
       <c r="I49" s="10"/>
       <c r="J49" s="10"/>
       <c r="K49" s="10"/>
-      <c r="L49" s="5"/>
+      <c r="L49" s="10"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="10"/>
+      <c r="Q49" s="10"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5"/>
@@ -1793,7 +2281,12 @@
       <c r="I50" s="10"/>
       <c r="J50" s="10"/>
       <c r="K50" s="10"/>
-      <c r="L50" s="5"/>
+      <c r="L50" s="10"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="10"/>
+      <c r="Q50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5"/>
@@ -1807,7 +2300,12 @@
       <c r="I51" s="10"/>
       <c r="J51" s="10"/>
       <c r="K51" s="10"/>
-      <c r="L51" s="5"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="10"/>
+      <c r="Q51" s="10"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5"/>
@@ -1821,7 +2319,12 @@
       <c r="I52" s="10"/>
       <c r="J52" s="10"/>
       <c r="K52" s="10"/>
-      <c r="L52" s="5"/>
+      <c r="L52" s="10"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="10"/>
+      <c r="Q52" s="10"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5"/>
@@ -1835,7 +2338,12 @@
       <c r="I53" s="10"/>
       <c r="J53" s="10"/>
       <c r="K53" s="10"/>
-      <c r="L53" s="5"/>
+      <c r="L53" s="10"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="10"/>
+      <c r="Q53" s="10"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5"/>
@@ -1849,7 +2357,12 @@
       <c r="I54" s="10"/>
       <c r="J54" s="10"/>
       <c r="K54" s="10"/>
-      <c r="L54" s="5"/>
+      <c r="L54" s="10"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="10"/>
+      <c r="Q54" s="10"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5"/>
@@ -1863,7 +2376,12 @@
       <c r="I55" s="10"/>
       <c r="J55" s="10"/>
       <c r="K55" s="10"/>
-      <c r="L55" s="5"/>
+      <c r="L55" s="10"/>
+      <c r="M55" s="10"/>
+      <c r="N55" s="5"/>
+      <c r="O55" s="5"/>
+      <c r="P55" s="10"/>
+      <c r="Q55" s="10"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5"/>
@@ -1877,7 +2395,12 @@
       <c r="I56" s="10"/>
       <c r="J56" s="10"/>
       <c r="K56" s="10"/>
-      <c r="L56" s="5"/>
+      <c r="L56" s="10"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="5"/>
+      <c r="O56" s="5"/>
+      <c r="P56" s="10"/>
+      <c r="Q56" s="10"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5"/>
@@ -1891,7 +2414,12 @@
       <c r="I57" s="10"/>
       <c r="J57" s="10"/>
       <c r="K57" s="10"/>
-      <c r="L57" s="5"/>
+      <c r="L57" s="10"/>
+      <c r="M57" s="10"/>
+      <c r="N57" s="5"/>
+      <c r="O57" s="5"/>
+      <c r="P57" s="10"/>
+      <c r="Q57" s="10"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5"/>
@@ -1905,7 +2433,12 @@
       <c r="I58" s="10"/>
       <c r="J58" s="10"/>
       <c r="K58" s="10"/>
-      <c r="L58" s="5"/>
+      <c r="L58" s="10"/>
+      <c r="M58" s="10"/>
+      <c r="N58" s="5"/>
+      <c r="O58" s="5"/>
+      <c r="P58" s="10"/>
+      <c r="Q58" s="10"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5"/>
@@ -1919,7 +2452,12 @@
       <c r="I59" s="10"/>
       <c r="J59" s="10"/>
       <c r="K59" s="10"/>
-      <c r="L59" s="5"/>
+      <c r="L59" s="10"/>
+      <c r="M59" s="10"/>
+      <c r="N59" s="5"/>
+      <c r="O59" s="5"/>
+      <c r="P59" s="10"/>
+      <c r="Q59" s="10"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5"/>
@@ -1933,7 +2471,12 @@
       <c r="I60" s="10"/>
       <c r="J60" s="10"/>
       <c r="K60" s="10"/>
-      <c r="L60" s="5"/>
+      <c r="L60" s="10"/>
+      <c r="M60" s="10"/>
+      <c r="N60" s="5"/>
+      <c r="O60" s="5"/>
+      <c r="P60" s="10"/>
+      <c r="Q60" s="10"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5"/>
@@ -1947,7 +2490,12 @@
       <c r="I61" s="10"/>
       <c r="J61" s="10"/>
       <c r="K61" s="10"/>
-      <c r="L61" s="5"/>
+      <c r="L61" s="10"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="5"/>
+      <c r="O61" s="5"/>
+      <c r="P61" s="10"/>
+      <c r="Q61" s="10"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5"/>
@@ -1961,7 +2509,12 @@
       <c r="I62" s="10"/>
       <c r="J62" s="10"/>
       <c r="K62" s="10"/>
-      <c r="L62" s="5"/>
+      <c r="L62" s="10"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="5"/>
+      <c r="O62" s="5"/>
+      <c r="P62" s="10"/>
+      <c r="Q62" s="10"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5"/>
@@ -1975,7 +2528,12 @@
       <c r="I63" s="10"/>
       <c r="J63" s="10"/>
       <c r="K63" s="10"/>
-      <c r="L63" s="5"/>
+      <c r="L63" s="10"/>
+      <c r="M63" s="10"/>
+      <c r="N63" s="5"/>
+      <c r="O63" s="5"/>
+      <c r="P63" s="10"/>
+      <c r="Q63" s="10"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5"/>
@@ -1989,7 +2547,12 @@
       <c r="I64" s="10"/>
       <c r="J64" s="10"/>
       <c r="K64" s="10"/>
-      <c r="L64" s="5"/>
+      <c r="L64" s="10"/>
+      <c r="M64" s="10"/>
+      <c r="N64" s="5"/>
+      <c r="O64" s="5"/>
+      <c r="P64" s="10"/>
+      <c r="Q64" s="10"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5"/>
@@ -2003,7 +2566,12 @@
       <c r="I65" s="10"/>
       <c r="J65" s="10"/>
       <c r="K65" s="10"/>
-      <c r="L65" s="5"/>
+      <c r="L65" s="10"/>
+      <c r="M65" s="10"/>
+      <c r="N65" s="5"/>
+      <c r="O65" s="5"/>
+      <c r="P65" s="10"/>
+      <c r="Q65" s="10"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5"/>
@@ -2017,7 +2585,12 @@
       <c r="I66" s="10"/>
       <c r="J66" s="10"/>
       <c r="K66" s="10"/>
-      <c r="L66" s="5"/>
+      <c r="L66" s="10"/>
+      <c r="M66" s="10"/>
+      <c r="N66" s="5"/>
+      <c r="O66" s="5"/>
+      <c r="P66" s="10"/>
+      <c r="Q66" s="10"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5"/>
@@ -2031,7 +2604,12 @@
       <c r="I67" s="10"/>
       <c r="J67" s="10"/>
       <c r="K67" s="10"/>
-      <c r="L67" s="5"/>
+      <c r="L67" s="10"/>
+      <c r="M67" s="10"/>
+      <c r="N67" s="5"/>
+      <c r="O67" s="5"/>
+      <c r="P67" s="10"/>
+      <c r="Q67" s="10"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5"/>
@@ -2045,7 +2623,12 @@
       <c r="I68" s="10"/>
       <c r="J68" s="10"/>
       <c r="K68" s="10"/>
-      <c r="L68" s="5"/>
+      <c r="L68" s="10"/>
+      <c r="M68" s="10"/>
+      <c r="N68" s="5"/>
+      <c r="O68" s="5"/>
+      <c r="P68" s="10"/>
+      <c r="Q68" s="10"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5"/>
@@ -2059,7 +2642,12 @@
       <c r="I69" s="10"/>
       <c r="J69" s="10"/>
       <c r="K69" s="10"/>
-      <c r="L69" s="5"/>
+      <c r="L69" s="10"/>
+      <c r="M69" s="10"/>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5"/>
+      <c r="P69" s="10"/>
+      <c r="Q69" s="10"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5"/>
@@ -2073,7 +2661,12 @@
       <c r="I70" s="10"/>
       <c r="J70" s="10"/>
       <c r="K70" s="10"/>
-      <c r="L70" s="5"/>
+      <c r="L70" s="10"/>
+      <c r="M70" s="10"/>
+      <c r="N70" s="5"/>
+      <c r="O70" s="5"/>
+      <c r="P70" s="10"/>
+      <c r="Q70" s="10"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5"/>
@@ -2087,7 +2680,12 @@
       <c r="I71" s="10"/>
       <c r="J71" s="10"/>
       <c r="K71" s="10"/>
-      <c r="L71" s="5"/>
+      <c r="L71" s="10"/>
+      <c r="M71" s="10"/>
+      <c r="N71" s="5"/>
+      <c r="O71" s="5"/>
+      <c r="P71" s="10"/>
+      <c r="Q71" s="10"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5"/>
@@ -2101,7 +2699,12 @@
       <c r="I72" s="10"/>
       <c r="J72" s="10"/>
       <c r="K72" s="10"/>
-      <c r="L72" s="5"/>
+      <c r="L72" s="10"/>
+      <c r="M72" s="10"/>
+      <c r="N72" s="5"/>
+      <c r="O72" s="5"/>
+      <c r="P72" s="10"/>
+      <c r="Q72" s="10"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5"/>
@@ -2115,7 +2718,12 @@
       <c r="I73" s="10"/>
       <c r="J73" s="10"/>
       <c r="K73" s="10"/>
-      <c r="L73" s="5"/>
+      <c r="L73" s="10"/>
+      <c r="M73" s="10"/>
+      <c r="N73" s="5"/>
+      <c r="O73" s="5"/>
+      <c r="P73" s="10"/>
+      <c r="Q73" s="10"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5"/>
@@ -2129,7 +2737,12 @@
       <c r="I74" s="10"/>
       <c r="J74" s="10"/>
       <c r="K74" s="10"/>
-      <c r="L74" s="5"/>
+      <c r="L74" s="10"/>
+      <c r="M74" s="10"/>
+      <c r="N74" s="5"/>
+      <c r="O74" s="5"/>
+      <c r="P74" s="10"/>
+      <c r="Q74" s="10"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5"/>
@@ -2143,7 +2756,12 @@
       <c r="I75" s="10"/>
       <c r="J75" s="10"/>
       <c r="K75" s="10"/>
-      <c r="L75" s="5"/>
+      <c r="L75" s="10"/>
+      <c r="M75" s="10"/>
+      <c r="N75" s="5"/>
+      <c r="O75" s="5"/>
+      <c r="P75" s="10"/>
+      <c r="Q75" s="10"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5"/>
@@ -2157,7 +2775,12 @@
       <c r="I76" s="10"/>
       <c r="J76" s="10"/>
       <c r="K76" s="10"/>
-      <c r="L76" s="5"/>
+      <c r="L76" s="10"/>
+      <c r="M76" s="10"/>
+      <c r="N76" s="5"/>
+      <c r="O76" s="5"/>
+      <c r="P76" s="10"/>
+      <c r="Q76" s="10"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5"/>
@@ -2171,7 +2794,12 @@
       <c r="I77" s="10"/>
       <c r="J77" s="10"/>
       <c r="K77" s="10"/>
-      <c r="L77" s="5"/>
+      <c r="L77" s="10"/>
+      <c r="M77" s="10"/>
+      <c r="N77" s="5"/>
+      <c r="O77" s="5"/>
+      <c r="P77" s="10"/>
+      <c r="Q77" s="10"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5"/>
@@ -2185,7 +2813,12 @@
       <c r="I78" s="10"/>
       <c r="J78" s="10"/>
       <c r="K78" s="10"/>
-      <c r="L78" s="5"/>
+      <c r="L78" s="10"/>
+      <c r="M78" s="10"/>
+      <c r="N78" s="5"/>
+      <c r="O78" s="5"/>
+      <c r="P78" s="10"/>
+      <c r="Q78" s="10"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5"/>
@@ -2199,7 +2832,12 @@
       <c r="I79" s="10"/>
       <c r="J79" s="10"/>
       <c r="K79" s="10"/>
-      <c r="L79" s="5"/>
+      <c r="L79" s="10"/>
+      <c r="M79" s="10"/>
+      <c r="N79" s="5"/>
+      <c r="O79" s="5"/>
+      <c r="P79" s="10"/>
+      <c r="Q79" s="10"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5"/>
@@ -2213,7 +2851,12 @@
       <c r="I80" s="10"/>
       <c r="J80" s="10"/>
       <c r="K80" s="10"/>
-      <c r="L80" s="5"/>
+      <c r="L80" s="10"/>
+      <c r="M80" s="10"/>
+      <c r="N80" s="5"/>
+      <c r="O80" s="5"/>
+      <c r="P80" s="10"/>
+      <c r="Q80" s="10"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5"/>
@@ -2227,7 +2870,12 @@
       <c r="I81" s="10"/>
       <c r="J81" s="10"/>
       <c r="K81" s="10"/>
-      <c r="L81" s="5"/>
+      <c r="L81" s="10"/>
+      <c r="M81" s="10"/>
+      <c r="N81" s="5"/>
+      <c r="O81" s="5"/>
+      <c r="P81" s="10"/>
+      <c r="Q81" s="10"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5"/>
@@ -2241,7 +2889,12 @@
       <c r="I82" s="10"/>
       <c r="J82" s="10"/>
       <c r="K82" s="10"/>
-      <c r="L82" s="5"/>
+      <c r="L82" s="10"/>
+      <c r="M82" s="10"/>
+      <c r="N82" s="5"/>
+      <c r="O82" s="5"/>
+      <c r="P82" s="10"/>
+      <c r="Q82" s="10"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5"/>
@@ -2255,7 +2908,12 @@
       <c r="I83" s="10"/>
       <c r="J83" s="10"/>
       <c r="K83" s="10"/>
-      <c r="L83" s="5"/>
+      <c r="L83" s="10"/>
+      <c r="M83" s="10"/>
+      <c r="N83" s="5"/>
+      <c r="O83" s="5"/>
+      <c r="P83" s="10"/>
+      <c r="Q83" s="10"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5"/>
@@ -2269,10 +2927,15 @@
       <c r="I84" s="10"/>
       <c r="J84" s="10"/>
       <c r="K84" s="10"/>
-      <c r="L84" s="5"/>
+      <c r="L84" s="10"/>
+      <c r="M84" s="10"/>
+      <c r="N84" s="5"/>
+      <c r="O84" s="5"/>
+      <c r="P84" s="10"/>
+      <c r="Q84" s="10"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A5:L84">
+  <conditionalFormatting sqref="A5:Q84">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$A5&lt;&gt;""</formula>
     </cfRule>
@@ -2282,13 +2945,13 @@
       <formula>$C5="P. Principal"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="8">
+  <dataValidations count="12">
     <dataValidation allowBlank="true" error="Elige un día del desplegable (Lunes … Domingo)." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A5:A84" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Elige un bloque del desplegable." errorStyle="stop" errorTitle="Bloque" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C5:C84" type="list">
-      <formula1>"Activación,P. Principal,Accesorios,Vuelta a la calma"</formula1>
+      <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Solo un número de 1 a 20." errorStyle="stop" errorTitle="Series" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E5:E84" type="whole">
@@ -2315,6 +2978,22 @@
       <formula1>"Sí"</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation allowBlank="true" error="Minutos del aeróbico (0,5 = 30 s)." errorStyle="stop" errorTitle="Minutos" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L5:L84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>600</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M5:M84" type="list">
+      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" errorTitle="RPE pre" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P5:P84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" errorTitle="RPE post" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q5:Q84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2332,7 +3011,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:Q84"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
@@ -2344,12 +3023,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="0" width="8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B1" s="11" t="n">
         <f aca="false">'Semana 1'!B1+7</f>
@@ -2362,46 +3045,61 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B2" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2416,7 +3114,12 @@
       <c r="I5" s="10"/>
       <c r="J5" s="10"/>
       <c r="K5" s="10"/>
-      <c r="L5" s="5"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
@@ -2430,7 +3133,12 @@
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
-      <c r="L6" s="5"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
@@ -2444,7 +3152,12 @@
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
-      <c r="L7" s="5"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
@@ -2458,7 +3171,12 @@
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
-      <c r="L8" s="5"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
@@ -2472,7 +3190,12 @@
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
-      <c r="L9" s="5"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
@@ -2486,7 +3209,12 @@
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
-      <c r="L10" s="5"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
@@ -2500,7 +3228,12 @@
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
-      <c r="L11" s="5"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
@@ -2514,7 +3247,12 @@
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
-      <c r="L12" s="5"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
@@ -2528,7 +3266,12 @@
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
-      <c r="L13" s="5"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
@@ -2542,7 +3285,12 @@
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
-      <c r="L14" s="5"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
@@ -2556,7 +3304,12 @@
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
-      <c r="L15" s="5"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5"/>
@@ -2570,7 +3323,12 @@
       <c r="I16" s="10"/>
       <c r="J16" s="10"/>
       <c r="K16" s="10"/>
-      <c r="L16" s="5"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5"/>
@@ -2584,7 +3342,12 @@
       <c r="I17" s="10"/>
       <c r="J17" s="10"/>
       <c r="K17" s="10"/>
-      <c r="L17" s="5"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5"/>
@@ -2598,7 +3361,12 @@
       <c r="I18" s="10"/>
       <c r="J18" s="10"/>
       <c r="K18" s="10"/>
-      <c r="L18" s="5"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5"/>
@@ -2612,7 +3380,12 @@
       <c r="I19" s="10"/>
       <c r="J19" s="10"/>
       <c r="K19" s="10"/>
-      <c r="L19" s="5"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5"/>
@@ -2626,7 +3399,12 @@
       <c r="I20" s="10"/>
       <c r="J20" s="10"/>
       <c r="K20" s="10"/>
-      <c r="L20" s="5"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5"/>
@@ -2640,7 +3418,12 @@
       <c r="I21" s="10"/>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
-      <c r="L21" s="5"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5"/>
@@ -2654,7 +3437,12 @@
       <c r="I22" s="10"/>
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
-      <c r="L22" s="5"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5"/>
@@ -2668,7 +3456,12 @@
       <c r="I23" s="10"/>
       <c r="J23" s="10"/>
       <c r="K23" s="10"/>
-      <c r="L23" s="5"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5"/>
@@ -2682,7 +3475,12 @@
       <c r="I24" s="10"/>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
-      <c r="L24" s="5"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5"/>
@@ -2696,7 +3494,12 @@
       <c r="I25" s="10"/>
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
-      <c r="L25" s="5"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5"/>
@@ -2710,7 +3513,12 @@
       <c r="I26" s="10"/>
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
-      <c r="L26" s="5"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5"/>
@@ -2724,7 +3532,12 @@
       <c r="I27" s="10"/>
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
-      <c r="L27" s="5"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5"/>
@@ -2738,7 +3551,12 @@
       <c r="I28" s="10"/>
       <c r="J28" s="10"/>
       <c r="K28" s="10"/>
-      <c r="L28" s="5"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5"/>
@@ -2752,7 +3570,12 @@
       <c r="I29" s="10"/>
       <c r="J29" s="10"/>
       <c r="K29" s="10"/>
-      <c r="L29" s="5"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5"/>
@@ -2766,7 +3589,12 @@
       <c r="I30" s="10"/>
       <c r="J30" s="10"/>
       <c r="K30" s="10"/>
-      <c r="L30" s="5"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="10"/>
+      <c r="Q30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5"/>
@@ -2780,7 +3608,12 @@
       <c r="I31" s="10"/>
       <c r="J31" s="10"/>
       <c r="K31" s="10"/>
-      <c r="L31" s="5"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="10"/>
+      <c r="Q31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5"/>
@@ -2794,7 +3627,12 @@
       <c r="I32" s="10"/>
       <c r="J32" s="10"/>
       <c r="K32" s="10"/>
-      <c r="L32" s="5"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="10"/>
+      <c r="Q32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5"/>
@@ -2808,7 +3646,12 @@
       <c r="I33" s="10"/>
       <c r="J33" s="10"/>
       <c r="K33" s="10"/>
-      <c r="L33" s="5"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="10"/>
+      <c r="Q33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5"/>
@@ -2822,7 +3665,12 @@
       <c r="I34" s="10"/>
       <c r="J34" s="10"/>
       <c r="K34" s="10"/>
-      <c r="L34" s="5"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5"/>
@@ -2836,7 +3684,12 @@
       <c r="I35" s="10"/>
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
-      <c r="L35" s="5"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5"/>
@@ -2850,7 +3703,12 @@
       <c r="I36" s="10"/>
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
-      <c r="L36" s="5"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="10"/>
+      <c r="Q36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5"/>
@@ -2864,7 +3722,12 @@
       <c r="I37" s="10"/>
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
-      <c r="L37" s="5"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5"/>
@@ -2878,7 +3741,12 @@
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
-      <c r="L38" s="5"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5"/>
@@ -2892,7 +3760,12 @@
       <c r="I39" s="10"/>
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
-      <c r="L39" s="5"/>
+      <c r="L39" s="10"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5"/>
@@ -2906,7 +3779,12 @@
       <c r="I40" s="10"/>
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
-      <c r="L40" s="5"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="10"/>
+      <c r="Q40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5"/>
@@ -2920,7 +3798,12 @@
       <c r="I41" s="10"/>
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
-      <c r="L41" s="5"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5"/>
@@ -2934,7 +3817,12 @@
       <c r="I42" s="10"/>
       <c r="J42" s="10"/>
       <c r="K42" s="10"/>
-      <c r="L42" s="5"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="10"/>
+      <c r="Q42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5"/>
@@ -2948,7 +3836,12 @@
       <c r="I43" s="10"/>
       <c r="J43" s="10"/>
       <c r="K43" s="10"/>
-      <c r="L43" s="5"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="10"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5"/>
@@ -2962,7 +3855,12 @@
       <c r="I44" s="10"/>
       <c r="J44" s="10"/>
       <c r="K44" s="10"/>
-      <c r="L44" s="5"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="10"/>
+      <c r="Q44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5"/>
@@ -2976,7 +3874,12 @@
       <c r="I45" s="10"/>
       <c r="J45" s="10"/>
       <c r="K45" s="10"/>
-      <c r="L45" s="5"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="10"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5"/>
@@ -2990,7 +3893,12 @@
       <c r="I46" s="10"/>
       <c r="J46" s="10"/>
       <c r="K46" s="10"/>
-      <c r="L46" s="5"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="10"/>
+      <c r="Q46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5"/>
@@ -3004,7 +3912,12 @@
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
       <c r="K47" s="10"/>
-      <c r="L47" s="5"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="10"/>
+      <c r="Q47" s="10"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5"/>
@@ -3018,7 +3931,12 @@
       <c r="I48" s="10"/>
       <c r="J48" s="10"/>
       <c r="K48" s="10"/>
-      <c r="L48" s="5"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="10"/>
+      <c r="Q48" s="10"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5"/>
@@ -3032,7 +3950,12 @@
       <c r="I49" s="10"/>
       <c r="J49" s="10"/>
       <c r="K49" s="10"/>
-      <c r="L49" s="5"/>
+      <c r="L49" s="10"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="10"/>
+      <c r="Q49" s="10"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5"/>
@@ -3046,7 +3969,12 @@
       <c r="I50" s="10"/>
       <c r="J50" s="10"/>
       <c r="K50" s="10"/>
-      <c r="L50" s="5"/>
+      <c r="L50" s="10"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="10"/>
+      <c r="Q50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5"/>
@@ -3060,7 +3988,12 @@
       <c r="I51" s="10"/>
       <c r="J51" s="10"/>
       <c r="K51" s="10"/>
-      <c r="L51" s="5"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="10"/>
+      <c r="Q51" s="10"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5"/>
@@ -3074,7 +4007,12 @@
       <c r="I52" s="10"/>
       <c r="J52" s="10"/>
       <c r="K52" s="10"/>
-      <c r="L52" s="5"/>
+      <c r="L52" s="10"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="10"/>
+      <c r="Q52" s="10"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5"/>
@@ -3088,7 +4026,12 @@
       <c r="I53" s="10"/>
       <c r="J53" s="10"/>
       <c r="K53" s="10"/>
-      <c r="L53" s="5"/>
+      <c r="L53" s="10"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="10"/>
+      <c r="Q53" s="10"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5"/>
@@ -3102,7 +4045,12 @@
       <c r="I54" s="10"/>
       <c r="J54" s="10"/>
       <c r="K54" s="10"/>
-      <c r="L54" s="5"/>
+      <c r="L54" s="10"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="10"/>
+      <c r="Q54" s="10"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5"/>
@@ -3116,7 +4064,12 @@
       <c r="I55" s="10"/>
       <c r="J55" s="10"/>
       <c r="K55" s="10"/>
-      <c r="L55" s="5"/>
+      <c r="L55" s="10"/>
+      <c r="M55" s="10"/>
+      <c r="N55" s="5"/>
+      <c r="O55" s="5"/>
+      <c r="P55" s="10"/>
+      <c r="Q55" s="10"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5"/>
@@ -3130,7 +4083,12 @@
       <c r="I56" s="10"/>
       <c r="J56" s="10"/>
       <c r="K56" s="10"/>
-      <c r="L56" s="5"/>
+      <c r="L56" s="10"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="5"/>
+      <c r="O56" s="5"/>
+      <c r="P56" s="10"/>
+      <c r="Q56" s="10"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5"/>
@@ -3144,7 +4102,12 @@
       <c r="I57" s="10"/>
       <c r="J57" s="10"/>
       <c r="K57" s="10"/>
-      <c r="L57" s="5"/>
+      <c r="L57" s="10"/>
+      <c r="M57" s="10"/>
+      <c r="N57" s="5"/>
+      <c r="O57" s="5"/>
+      <c r="P57" s="10"/>
+      <c r="Q57" s="10"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5"/>
@@ -3158,7 +4121,12 @@
       <c r="I58" s="10"/>
       <c r="J58" s="10"/>
       <c r="K58" s="10"/>
-      <c r="L58" s="5"/>
+      <c r="L58" s="10"/>
+      <c r="M58" s="10"/>
+      <c r="N58" s="5"/>
+      <c r="O58" s="5"/>
+      <c r="P58" s="10"/>
+      <c r="Q58" s="10"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5"/>
@@ -3172,7 +4140,12 @@
       <c r="I59" s="10"/>
       <c r="J59" s="10"/>
       <c r="K59" s="10"/>
-      <c r="L59" s="5"/>
+      <c r="L59" s="10"/>
+      <c r="M59" s="10"/>
+      <c r="N59" s="5"/>
+      <c r="O59" s="5"/>
+      <c r="P59" s="10"/>
+      <c r="Q59" s="10"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5"/>
@@ -3186,7 +4159,12 @@
       <c r="I60" s="10"/>
       <c r="J60" s="10"/>
       <c r="K60" s="10"/>
-      <c r="L60" s="5"/>
+      <c r="L60" s="10"/>
+      <c r="M60" s="10"/>
+      <c r="N60" s="5"/>
+      <c r="O60" s="5"/>
+      <c r="P60" s="10"/>
+      <c r="Q60" s="10"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5"/>
@@ -3200,7 +4178,12 @@
       <c r="I61" s="10"/>
       <c r="J61" s="10"/>
       <c r="K61" s="10"/>
-      <c r="L61" s="5"/>
+      <c r="L61" s="10"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="5"/>
+      <c r="O61" s="5"/>
+      <c r="P61" s="10"/>
+      <c r="Q61" s="10"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5"/>
@@ -3214,7 +4197,12 @@
       <c r="I62" s="10"/>
       <c r="J62" s="10"/>
       <c r="K62" s="10"/>
-      <c r="L62" s="5"/>
+      <c r="L62" s="10"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="5"/>
+      <c r="O62" s="5"/>
+      <c r="P62" s="10"/>
+      <c r="Q62" s="10"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5"/>
@@ -3228,7 +4216,12 @@
       <c r="I63" s="10"/>
       <c r="J63" s="10"/>
       <c r="K63" s="10"/>
-      <c r="L63" s="5"/>
+      <c r="L63" s="10"/>
+      <c r="M63" s="10"/>
+      <c r="N63" s="5"/>
+      <c r="O63" s="5"/>
+      <c r="P63" s="10"/>
+      <c r="Q63" s="10"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5"/>
@@ -3242,7 +4235,12 @@
       <c r="I64" s="10"/>
       <c r="J64" s="10"/>
       <c r="K64" s="10"/>
-      <c r="L64" s="5"/>
+      <c r="L64" s="10"/>
+      <c r="M64" s="10"/>
+      <c r="N64" s="5"/>
+      <c r="O64" s="5"/>
+      <c r="P64" s="10"/>
+      <c r="Q64" s="10"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5"/>
@@ -3256,7 +4254,12 @@
       <c r="I65" s="10"/>
       <c r="J65" s="10"/>
       <c r="K65" s="10"/>
-      <c r="L65" s="5"/>
+      <c r="L65" s="10"/>
+      <c r="M65" s="10"/>
+      <c r="N65" s="5"/>
+      <c r="O65" s="5"/>
+      <c r="P65" s="10"/>
+      <c r="Q65" s="10"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5"/>
@@ -3270,7 +4273,12 @@
       <c r="I66" s="10"/>
       <c r="J66" s="10"/>
       <c r="K66" s="10"/>
-      <c r="L66" s="5"/>
+      <c r="L66" s="10"/>
+      <c r="M66" s="10"/>
+      <c r="N66" s="5"/>
+      <c r="O66" s="5"/>
+      <c r="P66" s="10"/>
+      <c r="Q66" s="10"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5"/>
@@ -3284,7 +4292,12 @@
       <c r="I67" s="10"/>
       <c r="J67" s="10"/>
       <c r="K67" s="10"/>
-      <c r="L67" s="5"/>
+      <c r="L67" s="10"/>
+      <c r="M67" s="10"/>
+      <c r="N67" s="5"/>
+      <c r="O67" s="5"/>
+      <c r="P67" s="10"/>
+      <c r="Q67" s="10"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5"/>
@@ -3298,7 +4311,12 @@
       <c r="I68" s="10"/>
       <c r="J68" s="10"/>
       <c r="K68" s="10"/>
-      <c r="L68" s="5"/>
+      <c r="L68" s="10"/>
+      <c r="M68" s="10"/>
+      <c r="N68" s="5"/>
+      <c r="O68" s="5"/>
+      <c r="P68" s="10"/>
+      <c r="Q68" s="10"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5"/>
@@ -3312,7 +4330,12 @@
       <c r="I69" s="10"/>
       <c r="J69" s="10"/>
       <c r="K69" s="10"/>
-      <c r="L69" s="5"/>
+      <c r="L69" s="10"/>
+      <c r="M69" s="10"/>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5"/>
+      <c r="P69" s="10"/>
+      <c r="Q69" s="10"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5"/>
@@ -3326,7 +4349,12 @@
       <c r="I70" s="10"/>
       <c r="J70" s="10"/>
       <c r="K70" s="10"/>
-      <c r="L70" s="5"/>
+      <c r="L70" s="10"/>
+      <c r="M70" s="10"/>
+      <c r="N70" s="5"/>
+      <c r="O70" s="5"/>
+      <c r="P70" s="10"/>
+      <c r="Q70" s="10"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5"/>
@@ -3340,7 +4368,12 @@
       <c r="I71" s="10"/>
       <c r="J71" s="10"/>
       <c r="K71" s="10"/>
-      <c r="L71" s="5"/>
+      <c r="L71" s="10"/>
+      <c r="M71" s="10"/>
+      <c r="N71" s="5"/>
+      <c r="O71" s="5"/>
+      <c r="P71" s="10"/>
+      <c r="Q71" s="10"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5"/>
@@ -3354,7 +4387,12 @@
       <c r="I72" s="10"/>
       <c r="J72" s="10"/>
       <c r="K72" s="10"/>
-      <c r="L72" s="5"/>
+      <c r="L72" s="10"/>
+      <c r="M72" s="10"/>
+      <c r="N72" s="5"/>
+      <c r="O72" s="5"/>
+      <c r="P72" s="10"/>
+      <c r="Q72" s="10"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5"/>
@@ -3368,7 +4406,12 @@
       <c r="I73" s="10"/>
       <c r="J73" s="10"/>
       <c r="K73" s="10"/>
-      <c r="L73" s="5"/>
+      <c r="L73" s="10"/>
+      <c r="M73" s="10"/>
+      <c r="N73" s="5"/>
+      <c r="O73" s="5"/>
+      <c r="P73" s="10"/>
+      <c r="Q73" s="10"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5"/>
@@ -3382,7 +4425,12 @@
       <c r="I74" s="10"/>
       <c r="J74" s="10"/>
       <c r="K74" s="10"/>
-      <c r="L74" s="5"/>
+      <c r="L74" s="10"/>
+      <c r="M74" s="10"/>
+      <c r="N74" s="5"/>
+      <c r="O74" s="5"/>
+      <c r="P74" s="10"/>
+      <c r="Q74" s="10"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5"/>
@@ -3396,7 +4444,12 @@
       <c r="I75" s="10"/>
       <c r="J75" s="10"/>
       <c r="K75" s="10"/>
-      <c r="L75" s="5"/>
+      <c r="L75" s="10"/>
+      <c r="M75" s="10"/>
+      <c r="N75" s="5"/>
+      <c r="O75" s="5"/>
+      <c r="P75" s="10"/>
+      <c r="Q75" s="10"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5"/>
@@ -3410,7 +4463,12 @@
       <c r="I76" s="10"/>
       <c r="J76" s="10"/>
       <c r="K76" s="10"/>
-      <c r="L76" s="5"/>
+      <c r="L76" s="10"/>
+      <c r="M76" s="10"/>
+      <c r="N76" s="5"/>
+      <c r="O76" s="5"/>
+      <c r="P76" s="10"/>
+      <c r="Q76" s="10"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5"/>
@@ -3424,7 +4482,12 @@
       <c r="I77" s="10"/>
       <c r="J77" s="10"/>
       <c r="K77" s="10"/>
-      <c r="L77" s="5"/>
+      <c r="L77" s="10"/>
+      <c r="M77" s="10"/>
+      <c r="N77" s="5"/>
+      <c r="O77" s="5"/>
+      <c r="P77" s="10"/>
+      <c r="Q77" s="10"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5"/>
@@ -3438,7 +4501,12 @@
       <c r="I78" s="10"/>
       <c r="J78" s="10"/>
       <c r="K78" s="10"/>
-      <c r="L78" s="5"/>
+      <c r="L78" s="10"/>
+      <c r="M78" s="10"/>
+      <c r="N78" s="5"/>
+      <c r="O78" s="5"/>
+      <c r="P78" s="10"/>
+      <c r="Q78" s="10"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5"/>
@@ -3452,7 +4520,12 @@
       <c r="I79" s="10"/>
       <c r="J79" s="10"/>
       <c r="K79" s="10"/>
-      <c r="L79" s="5"/>
+      <c r="L79" s="10"/>
+      <c r="M79" s="10"/>
+      <c r="N79" s="5"/>
+      <c r="O79" s="5"/>
+      <c r="P79" s="10"/>
+      <c r="Q79" s="10"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5"/>
@@ -3466,7 +4539,12 @@
       <c r="I80" s="10"/>
       <c r="J80" s="10"/>
       <c r="K80" s="10"/>
-      <c r="L80" s="5"/>
+      <c r="L80" s="10"/>
+      <c r="M80" s="10"/>
+      <c r="N80" s="5"/>
+      <c r="O80" s="5"/>
+      <c r="P80" s="10"/>
+      <c r="Q80" s="10"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5"/>
@@ -3480,7 +4558,12 @@
       <c r="I81" s="10"/>
       <c r="J81" s="10"/>
       <c r="K81" s="10"/>
-      <c r="L81" s="5"/>
+      <c r="L81" s="10"/>
+      <c r="M81" s="10"/>
+      <c r="N81" s="5"/>
+      <c r="O81" s="5"/>
+      <c r="P81" s="10"/>
+      <c r="Q81" s="10"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5"/>
@@ -3494,7 +4577,12 @@
       <c r="I82" s="10"/>
       <c r="J82" s="10"/>
       <c r="K82" s="10"/>
-      <c r="L82" s="5"/>
+      <c r="L82" s="10"/>
+      <c r="M82" s="10"/>
+      <c r="N82" s="5"/>
+      <c r="O82" s="5"/>
+      <c r="P82" s="10"/>
+      <c r="Q82" s="10"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5"/>
@@ -3508,7 +4596,12 @@
       <c r="I83" s="10"/>
       <c r="J83" s="10"/>
       <c r="K83" s="10"/>
-      <c r="L83" s="5"/>
+      <c r="L83" s="10"/>
+      <c r="M83" s="10"/>
+      <c r="N83" s="5"/>
+      <c r="O83" s="5"/>
+      <c r="P83" s="10"/>
+      <c r="Q83" s="10"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5"/>
@@ -3522,10 +4615,15 @@
       <c r="I84" s="10"/>
       <c r="J84" s="10"/>
       <c r="K84" s="10"/>
-      <c r="L84" s="5"/>
+      <c r="L84" s="10"/>
+      <c r="M84" s="10"/>
+      <c r="N84" s="5"/>
+      <c r="O84" s="5"/>
+      <c r="P84" s="10"/>
+      <c r="Q84" s="10"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A5:L84">
+  <conditionalFormatting sqref="A5:Q84">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$A5&lt;&gt;""</formula>
     </cfRule>
@@ -3535,7 +4633,15 @@
       <formula>$C5="P. Principal"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="8">
+  <dataValidations count="12">
+    <dataValidation allowBlank="true" error="Elige un día del desplegable (Lunes … Domingo)." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A5:A84" type="list">
+      <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Elige un bloque del desplegable." errorStyle="stop" errorTitle="Bloque" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C5:C84" type="list">
+      <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Solo un número de 1 a 20." errorStyle="stop" errorTitle="Series" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E5:E84" type="whole">
       <formula1>1</formula1>
       <formula2>20</formula2>
@@ -3560,13 +4666,21 @@
       <formula1>"Sí"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige un día del desplegable (Lunes … Domingo)." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A5:A84" type="list">
-      <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
+    <dataValidation allowBlank="true" error="Minutos del aeróbico (0,5 = 30 s)." errorStyle="stop" errorTitle="Minutos" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L5:L84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>600</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M5:M84" type="list">
+      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige un bloque del desplegable." errorStyle="stop" errorTitle="Bloque" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C5:C84" type="list">
-      <formula1>"Activación,P. Principal,Accesorios,Vuelta a la calma"</formula1>
-      <formula2>0</formula2>
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" errorTitle="RPE pre" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P5:P84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" errorTitle="RPE post" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q5:Q84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>10</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3584,7 +4698,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:Q84"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
@@ -3596,12 +4710,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="0" width="8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B1" s="11" t="n">
         <f aca="false">'Semana 2'!B1+7</f>
@@ -3614,46 +4732,61 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B2" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3668,7 +4801,12 @@
       <c r="I5" s="10"/>
       <c r="J5" s="10"/>
       <c r="K5" s="10"/>
-      <c r="L5" s="5"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
@@ -3682,7 +4820,12 @@
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
-      <c r="L6" s="5"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
@@ -3696,7 +4839,12 @@
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
-      <c r="L7" s="5"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
@@ -3710,7 +4858,12 @@
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
-      <c r="L8" s="5"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
@@ -3724,7 +4877,12 @@
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
-      <c r="L9" s="5"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
@@ -3738,7 +4896,12 @@
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
-      <c r="L10" s="5"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
@@ -3752,7 +4915,12 @@
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
-      <c r="L11" s="5"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
@@ -3766,7 +4934,12 @@
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
-      <c r="L12" s="5"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
@@ -3780,7 +4953,12 @@
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
-      <c r="L13" s="5"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
@@ -3794,7 +4972,12 @@
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
-      <c r="L14" s="5"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
@@ -3808,7 +4991,12 @@
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
-      <c r="L15" s="5"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5"/>
@@ -3822,7 +5010,12 @@
       <c r="I16" s="10"/>
       <c r="J16" s="10"/>
       <c r="K16" s="10"/>
-      <c r="L16" s="5"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5"/>
@@ -3836,7 +5029,12 @@
       <c r="I17" s="10"/>
       <c r="J17" s="10"/>
       <c r="K17" s="10"/>
-      <c r="L17" s="5"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5"/>
@@ -3850,7 +5048,12 @@
       <c r="I18" s="10"/>
       <c r="J18" s="10"/>
       <c r="K18" s="10"/>
-      <c r="L18" s="5"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5"/>
@@ -3864,7 +5067,12 @@
       <c r="I19" s="10"/>
       <c r="J19" s="10"/>
       <c r="K19" s="10"/>
-      <c r="L19" s="5"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5"/>
@@ -3878,7 +5086,12 @@
       <c r="I20" s="10"/>
       <c r="J20" s="10"/>
       <c r="K20" s="10"/>
-      <c r="L20" s="5"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5"/>
@@ -3892,7 +5105,12 @@
       <c r="I21" s="10"/>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
-      <c r="L21" s="5"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5"/>
@@ -3906,7 +5124,12 @@
       <c r="I22" s="10"/>
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
-      <c r="L22" s="5"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5"/>
@@ -3920,7 +5143,12 @@
       <c r="I23" s="10"/>
       <c r="J23" s="10"/>
       <c r="K23" s="10"/>
-      <c r="L23" s="5"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5"/>
@@ -3934,7 +5162,12 @@
       <c r="I24" s="10"/>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
-      <c r="L24" s="5"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5"/>
@@ -3948,7 +5181,12 @@
       <c r="I25" s="10"/>
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
-      <c r="L25" s="5"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5"/>
@@ -3962,7 +5200,12 @@
       <c r="I26" s="10"/>
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
-      <c r="L26" s="5"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5"/>
@@ -3976,7 +5219,12 @@
       <c r="I27" s="10"/>
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
-      <c r="L27" s="5"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5"/>
@@ -3990,7 +5238,12 @@
       <c r="I28" s="10"/>
       <c r="J28" s="10"/>
       <c r="K28" s="10"/>
-      <c r="L28" s="5"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5"/>
@@ -4004,7 +5257,12 @@
       <c r="I29" s="10"/>
       <c r="J29" s="10"/>
       <c r="K29" s="10"/>
-      <c r="L29" s="5"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5"/>
@@ -4018,7 +5276,12 @@
       <c r="I30" s="10"/>
       <c r="J30" s="10"/>
       <c r="K30" s="10"/>
-      <c r="L30" s="5"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="10"/>
+      <c r="Q30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5"/>
@@ -4032,7 +5295,12 @@
       <c r="I31" s="10"/>
       <c r="J31" s="10"/>
       <c r="K31" s="10"/>
-      <c r="L31" s="5"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="10"/>
+      <c r="Q31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5"/>
@@ -4046,7 +5314,12 @@
       <c r="I32" s="10"/>
       <c r="J32" s="10"/>
       <c r="K32" s="10"/>
-      <c r="L32" s="5"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="10"/>
+      <c r="Q32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5"/>
@@ -4060,7 +5333,12 @@
       <c r="I33" s="10"/>
       <c r="J33" s="10"/>
       <c r="K33" s="10"/>
-      <c r="L33" s="5"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="10"/>
+      <c r="Q33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5"/>
@@ -4074,7 +5352,12 @@
       <c r="I34" s="10"/>
       <c r="J34" s="10"/>
       <c r="K34" s="10"/>
-      <c r="L34" s="5"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5"/>
@@ -4088,7 +5371,12 @@
       <c r="I35" s="10"/>
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
-      <c r="L35" s="5"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5"/>
@@ -4102,7 +5390,12 @@
       <c r="I36" s="10"/>
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
-      <c r="L36" s="5"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="10"/>
+      <c r="Q36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5"/>
@@ -4116,7 +5409,12 @@
       <c r="I37" s="10"/>
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
-      <c r="L37" s="5"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5"/>
@@ -4130,7 +5428,12 @@
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
-      <c r="L38" s="5"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5"/>
@@ -4144,7 +5447,12 @@
       <c r="I39" s="10"/>
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
-      <c r="L39" s="5"/>
+      <c r="L39" s="10"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5"/>
@@ -4158,7 +5466,12 @@
       <c r="I40" s="10"/>
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
-      <c r="L40" s="5"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="10"/>
+      <c r="Q40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5"/>
@@ -4172,7 +5485,12 @@
       <c r="I41" s="10"/>
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
-      <c r="L41" s="5"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5"/>
@@ -4186,7 +5504,12 @@
       <c r="I42" s="10"/>
       <c r="J42" s="10"/>
       <c r="K42" s="10"/>
-      <c r="L42" s="5"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="10"/>
+      <c r="Q42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5"/>
@@ -4200,7 +5523,12 @@
       <c r="I43" s="10"/>
       <c r="J43" s="10"/>
       <c r="K43" s="10"/>
-      <c r="L43" s="5"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="10"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5"/>
@@ -4214,7 +5542,12 @@
       <c r="I44" s="10"/>
       <c r="J44" s="10"/>
       <c r="K44" s="10"/>
-      <c r="L44" s="5"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="10"/>
+      <c r="Q44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5"/>
@@ -4228,7 +5561,12 @@
       <c r="I45" s="10"/>
       <c r="J45" s="10"/>
       <c r="K45" s="10"/>
-      <c r="L45" s="5"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="10"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5"/>
@@ -4242,7 +5580,12 @@
       <c r="I46" s="10"/>
       <c r="J46" s="10"/>
       <c r="K46" s="10"/>
-      <c r="L46" s="5"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="10"/>
+      <c r="Q46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5"/>
@@ -4256,7 +5599,12 @@
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
       <c r="K47" s="10"/>
-      <c r="L47" s="5"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="10"/>
+      <c r="Q47" s="10"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5"/>
@@ -4270,7 +5618,12 @@
       <c r="I48" s="10"/>
       <c r="J48" s="10"/>
       <c r="K48" s="10"/>
-      <c r="L48" s="5"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="10"/>
+      <c r="Q48" s="10"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5"/>
@@ -4284,7 +5637,12 @@
       <c r="I49" s="10"/>
       <c r="J49" s="10"/>
       <c r="K49" s="10"/>
-      <c r="L49" s="5"/>
+      <c r="L49" s="10"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="10"/>
+      <c r="Q49" s="10"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5"/>
@@ -4298,7 +5656,12 @@
       <c r="I50" s="10"/>
       <c r="J50" s="10"/>
       <c r="K50" s="10"/>
-      <c r="L50" s="5"/>
+      <c r="L50" s="10"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="10"/>
+      <c r="Q50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5"/>
@@ -4312,7 +5675,12 @@
       <c r="I51" s="10"/>
       <c r="J51" s="10"/>
       <c r="K51" s="10"/>
-      <c r="L51" s="5"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="10"/>
+      <c r="Q51" s="10"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5"/>
@@ -4326,7 +5694,12 @@
       <c r="I52" s="10"/>
       <c r="J52" s="10"/>
       <c r="K52" s="10"/>
-      <c r="L52" s="5"/>
+      <c r="L52" s="10"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="10"/>
+      <c r="Q52" s="10"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5"/>
@@ -4340,7 +5713,12 @@
       <c r="I53" s="10"/>
       <c r="J53" s="10"/>
       <c r="K53" s="10"/>
-      <c r="L53" s="5"/>
+      <c r="L53" s="10"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="10"/>
+      <c r="Q53" s="10"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5"/>
@@ -4354,7 +5732,12 @@
       <c r="I54" s="10"/>
       <c r="J54" s="10"/>
       <c r="K54" s="10"/>
-      <c r="L54" s="5"/>
+      <c r="L54" s="10"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="10"/>
+      <c r="Q54" s="10"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5"/>
@@ -4368,7 +5751,12 @@
       <c r="I55" s="10"/>
       <c r="J55" s="10"/>
       <c r="K55" s="10"/>
-      <c r="L55" s="5"/>
+      <c r="L55" s="10"/>
+      <c r="M55" s="10"/>
+      <c r="N55" s="5"/>
+      <c r="O55" s="5"/>
+      <c r="P55" s="10"/>
+      <c r="Q55" s="10"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5"/>
@@ -4382,7 +5770,12 @@
       <c r="I56" s="10"/>
       <c r="J56" s="10"/>
       <c r="K56" s="10"/>
-      <c r="L56" s="5"/>
+      <c r="L56" s="10"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="5"/>
+      <c r="O56" s="5"/>
+      <c r="P56" s="10"/>
+      <c r="Q56" s="10"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5"/>
@@ -4396,7 +5789,12 @@
       <c r="I57" s="10"/>
       <c r="J57" s="10"/>
       <c r="K57" s="10"/>
-      <c r="L57" s="5"/>
+      <c r="L57" s="10"/>
+      <c r="M57" s="10"/>
+      <c r="N57" s="5"/>
+      <c r="O57" s="5"/>
+      <c r="P57" s="10"/>
+      <c r="Q57" s="10"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5"/>
@@ -4410,7 +5808,12 @@
       <c r="I58" s="10"/>
       <c r="J58" s="10"/>
       <c r="K58" s="10"/>
-      <c r="L58" s="5"/>
+      <c r="L58" s="10"/>
+      <c r="M58" s="10"/>
+      <c r="N58" s="5"/>
+      <c r="O58" s="5"/>
+      <c r="P58" s="10"/>
+      <c r="Q58" s="10"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5"/>
@@ -4424,7 +5827,12 @@
       <c r="I59" s="10"/>
       <c r="J59" s="10"/>
       <c r="K59" s="10"/>
-      <c r="L59" s="5"/>
+      <c r="L59" s="10"/>
+      <c r="M59" s="10"/>
+      <c r="N59" s="5"/>
+      <c r="O59" s="5"/>
+      <c r="P59" s="10"/>
+      <c r="Q59" s="10"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5"/>
@@ -4438,7 +5846,12 @@
       <c r="I60" s="10"/>
       <c r="J60" s="10"/>
       <c r="K60" s="10"/>
-      <c r="L60" s="5"/>
+      <c r="L60" s="10"/>
+      <c r="M60" s="10"/>
+      <c r="N60" s="5"/>
+      <c r="O60" s="5"/>
+      <c r="P60" s="10"/>
+      <c r="Q60" s="10"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5"/>
@@ -4452,7 +5865,12 @@
       <c r="I61" s="10"/>
       <c r="J61" s="10"/>
       <c r="K61" s="10"/>
-      <c r="L61" s="5"/>
+      <c r="L61" s="10"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="5"/>
+      <c r="O61" s="5"/>
+      <c r="P61" s="10"/>
+      <c r="Q61" s="10"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5"/>
@@ -4466,7 +5884,12 @@
       <c r="I62" s="10"/>
       <c r="J62" s="10"/>
       <c r="K62" s="10"/>
-      <c r="L62" s="5"/>
+      <c r="L62" s="10"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="5"/>
+      <c r="O62" s="5"/>
+      <c r="P62" s="10"/>
+      <c r="Q62" s="10"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5"/>
@@ -4480,7 +5903,12 @@
       <c r="I63" s="10"/>
       <c r="J63" s="10"/>
       <c r="K63" s="10"/>
-      <c r="L63" s="5"/>
+      <c r="L63" s="10"/>
+      <c r="M63" s="10"/>
+      <c r="N63" s="5"/>
+      <c r="O63" s="5"/>
+      <c r="P63" s="10"/>
+      <c r="Q63" s="10"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5"/>
@@ -4494,7 +5922,12 @@
       <c r="I64" s="10"/>
       <c r="J64" s="10"/>
       <c r="K64" s="10"/>
-      <c r="L64" s="5"/>
+      <c r="L64" s="10"/>
+      <c r="M64" s="10"/>
+      <c r="N64" s="5"/>
+      <c r="O64" s="5"/>
+      <c r="P64" s="10"/>
+      <c r="Q64" s="10"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5"/>
@@ -4508,7 +5941,12 @@
       <c r="I65" s="10"/>
       <c r="J65" s="10"/>
       <c r="K65" s="10"/>
-      <c r="L65" s="5"/>
+      <c r="L65" s="10"/>
+      <c r="M65" s="10"/>
+      <c r="N65" s="5"/>
+      <c r="O65" s="5"/>
+      <c r="P65" s="10"/>
+      <c r="Q65" s="10"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5"/>
@@ -4522,7 +5960,12 @@
       <c r="I66" s="10"/>
       <c r="J66" s="10"/>
       <c r="K66" s="10"/>
-      <c r="L66" s="5"/>
+      <c r="L66" s="10"/>
+      <c r="M66" s="10"/>
+      <c r="N66" s="5"/>
+      <c r="O66" s="5"/>
+      <c r="P66" s="10"/>
+      <c r="Q66" s="10"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5"/>
@@ -4536,7 +5979,12 @@
       <c r="I67" s="10"/>
       <c r="J67" s="10"/>
       <c r="K67" s="10"/>
-      <c r="L67" s="5"/>
+      <c r="L67" s="10"/>
+      <c r="M67" s="10"/>
+      <c r="N67" s="5"/>
+      <c r="O67" s="5"/>
+      <c r="P67" s="10"/>
+      <c r="Q67" s="10"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5"/>
@@ -4550,7 +5998,12 @@
       <c r="I68" s="10"/>
       <c r="J68" s="10"/>
       <c r="K68" s="10"/>
-      <c r="L68" s="5"/>
+      <c r="L68" s="10"/>
+      <c r="M68" s="10"/>
+      <c r="N68" s="5"/>
+      <c r="O68" s="5"/>
+      <c r="P68" s="10"/>
+      <c r="Q68" s="10"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5"/>
@@ -4564,7 +6017,12 @@
       <c r="I69" s="10"/>
       <c r="J69" s="10"/>
       <c r="K69" s="10"/>
-      <c r="L69" s="5"/>
+      <c r="L69" s="10"/>
+      <c r="M69" s="10"/>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5"/>
+      <c r="P69" s="10"/>
+      <c r="Q69" s="10"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5"/>
@@ -4578,7 +6036,12 @@
       <c r="I70" s="10"/>
       <c r="J70" s="10"/>
       <c r="K70" s="10"/>
-      <c r="L70" s="5"/>
+      <c r="L70" s="10"/>
+      <c r="M70" s="10"/>
+      <c r="N70" s="5"/>
+      <c r="O70" s="5"/>
+      <c r="P70" s="10"/>
+      <c r="Q70" s="10"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5"/>
@@ -4592,7 +6055,12 @@
       <c r="I71" s="10"/>
       <c r="J71" s="10"/>
       <c r="K71" s="10"/>
-      <c r="L71" s="5"/>
+      <c r="L71" s="10"/>
+      <c r="M71" s="10"/>
+      <c r="N71" s="5"/>
+      <c r="O71" s="5"/>
+      <c r="P71" s="10"/>
+      <c r="Q71" s="10"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5"/>
@@ -4606,7 +6074,12 @@
       <c r="I72" s="10"/>
       <c r="J72" s="10"/>
       <c r="K72" s="10"/>
-      <c r="L72" s="5"/>
+      <c r="L72" s="10"/>
+      <c r="M72" s="10"/>
+      <c r="N72" s="5"/>
+      <c r="O72" s="5"/>
+      <c r="P72" s="10"/>
+      <c r="Q72" s="10"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5"/>
@@ -4620,7 +6093,12 @@
       <c r="I73" s="10"/>
       <c r="J73" s="10"/>
       <c r="K73" s="10"/>
-      <c r="L73" s="5"/>
+      <c r="L73" s="10"/>
+      <c r="M73" s="10"/>
+      <c r="N73" s="5"/>
+      <c r="O73" s="5"/>
+      <c r="P73" s="10"/>
+      <c r="Q73" s="10"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5"/>
@@ -4634,7 +6112,12 @@
       <c r="I74" s="10"/>
       <c r="J74" s="10"/>
       <c r="K74" s="10"/>
-      <c r="L74" s="5"/>
+      <c r="L74" s="10"/>
+      <c r="M74" s="10"/>
+      <c r="N74" s="5"/>
+      <c r="O74" s="5"/>
+      <c r="P74" s="10"/>
+      <c r="Q74" s="10"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5"/>
@@ -4648,7 +6131,12 @@
       <c r="I75" s="10"/>
       <c r="J75" s="10"/>
       <c r="K75" s="10"/>
-      <c r="L75" s="5"/>
+      <c r="L75" s="10"/>
+      <c r="M75" s="10"/>
+      <c r="N75" s="5"/>
+      <c r="O75" s="5"/>
+      <c r="P75" s="10"/>
+      <c r="Q75" s="10"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5"/>
@@ -4662,7 +6150,12 @@
       <c r="I76" s="10"/>
       <c r="J76" s="10"/>
       <c r="K76" s="10"/>
-      <c r="L76" s="5"/>
+      <c r="L76" s="10"/>
+      <c r="M76" s="10"/>
+      <c r="N76" s="5"/>
+      <c r="O76" s="5"/>
+      <c r="P76" s="10"/>
+      <c r="Q76" s="10"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5"/>
@@ -4676,7 +6169,12 @@
       <c r="I77" s="10"/>
       <c r="J77" s="10"/>
       <c r="K77" s="10"/>
-      <c r="L77" s="5"/>
+      <c r="L77" s="10"/>
+      <c r="M77" s="10"/>
+      <c r="N77" s="5"/>
+      <c r="O77" s="5"/>
+      <c r="P77" s="10"/>
+      <c r="Q77" s="10"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5"/>
@@ -4690,7 +6188,12 @@
       <c r="I78" s="10"/>
       <c r="J78" s="10"/>
       <c r="K78" s="10"/>
-      <c r="L78" s="5"/>
+      <c r="L78" s="10"/>
+      <c r="M78" s="10"/>
+      <c r="N78" s="5"/>
+      <c r="O78" s="5"/>
+      <c r="P78" s="10"/>
+      <c r="Q78" s="10"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5"/>
@@ -4704,7 +6207,12 @@
       <c r="I79" s="10"/>
       <c r="J79" s="10"/>
       <c r="K79" s="10"/>
-      <c r="L79" s="5"/>
+      <c r="L79" s="10"/>
+      <c r="M79" s="10"/>
+      <c r="N79" s="5"/>
+      <c r="O79" s="5"/>
+      <c r="P79" s="10"/>
+      <c r="Q79" s="10"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5"/>
@@ -4718,7 +6226,12 @@
       <c r="I80" s="10"/>
       <c r="J80" s="10"/>
       <c r="K80" s="10"/>
-      <c r="L80" s="5"/>
+      <c r="L80" s="10"/>
+      <c r="M80" s="10"/>
+      <c r="N80" s="5"/>
+      <c r="O80" s="5"/>
+      <c r="P80" s="10"/>
+      <c r="Q80" s="10"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5"/>
@@ -4732,7 +6245,12 @@
       <c r="I81" s="10"/>
       <c r="J81" s="10"/>
       <c r="K81" s="10"/>
-      <c r="L81" s="5"/>
+      <c r="L81" s="10"/>
+      <c r="M81" s="10"/>
+      <c r="N81" s="5"/>
+      <c r="O81" s="5"/>
+      <c r="P81" s="10"/>
+      <c r="Q81" s="10"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5"/>
@@ -4746,7 +6264,12 @@
       <c r="I82" s="10"/>
       <c r="J82" s="10"/>
       <c r="K82" s="10"/>
-      <c r="L82" s="5"/>
+      <c r="L82" s="10"/>
+      <c r="M82" s="10"/>
+      <c r="N82" s="5"/>
+      <c r="O82" s="5"/>
+      <c r="P82" s="10"/>
+      <c r="Q82" s="10"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5"/>
@@ -4760,7 +6283,12 @@
       <c r="I83" s="10"/>
       <c r="J83" s="10"/>
       <c r="K83" s="10"/>
-      <c r="L83" s="5"/>
+      <c r="L83" s="10"/>
+      <c r="M83" s="10"/>
+      <c r="N83" s="5"/>
+      <c r="O83" s="5"/>
+      <c r="P83" s="10"/>
+      <c r="Q83" s="10"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5"/>
@@ -4774,10 +6302,15 @@
       <c r="I84" s="10"/>
       <c r="J84" s="10"/>
       <c r="K84" s="10"/>
-      <c r="L84" s="5"/>
+      <c r="L84" s="10"/>
+      <c r="M84" s="10"/>
+      <c r="N84" s="5"/>
+      <c r="O84" s="5"/>
+      <c r="P84" s="10"/>
+      <c r="Q84" s="10"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A5:L84">
+  <conditionalFormatting sqref="A5:Q84">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$A5&lt;&gt;""</formula>
     </cfRule>
@@ -4787,7 +6320,7 @@
       <formula>$C5="P. Principal"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="8">
+  <dataValidations count="12">
     <dataValidation allowBlank="true" error="Solo un número de 1 a 20." errorStyle="stop" errorTitle="Series" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E5:E84" type="whole">
       <formula1>1</formula1>
       <formula2>20</formula2>
@@ -4812,12 +6345,28 @@
       <formula1>"Sí"</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation allowBlank="true" error="Minutos del aeróbico (0,5 = 30 s)." errorStyle="stop" errorTitle="Minutos" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L5:L84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>600</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" errorTitle="RPE pre" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P5:P84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" errorTitle="RPE post" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q5:Q84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable (Lunes … Domingo)." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A5:A84" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Elige un bloque del desplegable." errorStyle="stop" errorTitle="Bloque" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C5:C84" type="list">
-      <formula1>"Activación,P. Principal,Accesorios,Vuelta a la calma"</formula1>
+      <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M5:M84" type="list">
+      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -4836,7 +6385,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:Q84"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
@@ -4848,12 +6397,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="0" width="8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B1" s="11" t="n">
         <f aca="false">'Semana 3'!B1+7</f>
@@ -4866,46 +6419,61 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B2" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4920,7 +6488,12 @@
       <c r="I5" s="10"/>
       <c r="J5" s="10"/>
       <c r="K5" s="10"/>
-      <c r="L5" s="5"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
@@ -4934,7 +6507,12 @@
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
-      <c r="L6" s="5"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
@@ -4948,7 +6526,12 @@
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
-      <c r="L7" s="5"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
@@ -4962,7 +6545,12 @@
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
-      <c r="L8" s="5"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
@@ -4976,7 +6564,12 @@
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
-      <c r="L9" s="5"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
@@ -4990,7 +6583,12 @@
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
-      <c r="L10" s="5"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
@@ -5004,7 +6602,12 @@
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
-      <c r="L11" s="5"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
@@ -5018,7 +6621,12 @@
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
-      <c r="L12" s="5"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
@@ -5032,7 +6640,12 @@
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
-      <c r="L13" s="5"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
@@ -5046,7 +6659,12 @@
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
-      <c r="L14" s="5"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
@@ -5060,7 +6678,12 @@
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
-      <c r="L15" s="5"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5"/>
@@ -5074,7 +6697,12 @@
       <c r="I16" s="10"/>
       <c r="J16" s="10"/>
       <c r="K16" s="10"/>
-      <c r="L16" s="5"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5"/>
@@ -5088,7 +6716,12 @@
       <c r="I17" s="10"/>
       <c r="J17" s="10"/>
       <c r="K17" s="10"/>
-      <c r="L17" s="5"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5"/>
@@ -5102,7 +6735,12 @@
       <c r="I18" s="10"/>
       <c r="J18" s="10"/>
       <c r="K18" s="10"/>
-      <c r="L18" s="5"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5"/>
@@ -5116,7 +6754,12 @@
       <c r="I19" s="10"/>
       <c r="J19" s="10"/>
       <c r="K19" s="10"/>
-      <c r="L19" s="5"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5"/>
@@ -5130,7 +6773,12 @@
       <c r="I20" s="10"/>
       <c r="J20" s="10"/>
       <c r="K20" s="10"/>
-      <c r="L20" s="5"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5"/>
@@ -5144,7 +6792,12 @@
       <c r="I21" s="10"/>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
-      <c r="L21" s="5"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5"/>
@@ -5158,7 +6811,12 @@
       <c r="I22" s="10"/>
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
-      <c r="L22" s="5"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5"/>
@@ -5172,7 +6830,12 @@
       <c r="I23" s="10"/>
       <c r="J23" s="10"/>
       <c r="K23" s="10"/>
-      <c r="L23" s="5"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5"/>
@@ -5186,7 +6849,12 @@
       <c r="I24" s="10"/>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
-      <c r="L24" s="5"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5"/>
@@ -5200,7 +6868,12 @@
       <c r="I25" s="10"/>
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
-      <c r="L25" s="5"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5"/>
@@ -5214,7 +6887,12 @@
       <c r="I26" s="10"/>
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
-      <c r="L26" s="5"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5"/>
@@ -5228,7 +6906,12 @@
       <c r="I27" s="10"/>
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
-      <c r="L27" s="5"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5"/>
@@ -5242,7 +6925,12 @@
       <c r="I28" s="10"/>
       <c r="J28" s="10"/>
       <c r="K28" s="10"/>
-      <c r="L28" s="5"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5"/>
@@ -5256,7 +6944,12 @@
       <c r="I29" s="10"/>
       <c r="J29" s="10"/>
       <c r="K29" s="10"/>
-      <c r="L29" s="5"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5"/>
@@ -5270,7 +6963,12 @@
       <c r="I30" s="10"/>
       <c r="J30" s="10"/>
       <c r="K30" s="10"/>
-      <c r="L30" s="5"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="10"/>
+      <c r="Q30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5"/>
@@ -5284,7 +6982,12 @@
       <c r="I31" s="10"/>
       <c r="J31" s="10"/>
       <c r="K31" s="10"/>
-      <c r="L31" s="5"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="10"/>
+      <c r="Q31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5"/>
@@ -5298,7 +7001,12 @@
       <c r="I32" s="10"/>
       <c r="J32" s="10"/>
       <c r="K32" s="10"/>
-      <c r="L32" s="5"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="10"/>
+      <c r="Q32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5"/>
@@ -5312,7 +7020,12 @@
       <c r="I33" s="10"/>
       <c r="J33" s="10"/>
       <c r="K33" s="10"/>
-      <c r="L33" s="5"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="10"/>
+      <c r="Q33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5"/>
@@ -5326,7 +7039,12 @@
       <c r="I34" s="10"/>
       <c r="J34" s="10"/>
       <c r="K34" s="10"/>
-      <c r="L34" s="5"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5"/>
@@ -5340,7 +7058,12 @@
       <c r="I35" s="10"/>
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
-      <c r="L35" s="5"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5"/>
@@ -5354,7 +7077,12 @@
       <c r="I36" s="10"/>
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
-      <c r="L36" s="5"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="10"/>
+      <c r="Q36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5"/>
@@ -5368,7 +7096,12 @@
       <c r="I37" s="10"/>
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
-      <c r="L37" s="5"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5"/>
@@ -5382,7 +7115,12 @@
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
-      <c r="L38" s="5"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5"/>
@@ -5396,7 +7134,12 @@
       <c r="I39" s="10"/>
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
-      <c r="L39" s="5"/>
+      <c r="L39" s="10"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5"/>
@@ -5410,7 +7153,12 @@
       <c r="I40" s="10"/>
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
-      <c r="L40" s="5"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="10"/>
+      <c r="Q40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5"/>
@@ -5424,7 +7172,12 @@
       <c r="I41" s="10"/>
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
-      <c r="L41" s="5"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5"/>
@@ -5438,7 +7191,12 @@
       <c r="I42" s="10"/>
       <c r="J42" s="10"/>
       <c r="K42" s="10"/>
-      <c r="L42" s="5"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="10"/>
+      <c r="Q42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5"/>
@@ -5452,7 +7210,12 @@
       <c r="I43" s="10"/>
       <c r="J43" s="10"/>
       <c r="K43" s="10"/>
-      <c r="L43" s="5"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="10"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5"/>
@@ -5466,7 +7229,12 @@
       <c r="I44" s="10"/>
       <c r="J44" s="10"/>
       <c r="K44" s="10"/>
-      <c r="L44" s="5"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="10"/>
+      <c r="Q44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5"/>
@@ -5480,7 +7248,12 @@
       <c r="I45" s="10"/>
       <c r="J45" s="10"/>
       <c r="K45" s="10"/>
-      <c r="L45" s="5"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="10"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5"/>
@@ -5494,7 +7267,12 @@
       <c r="I46" s="10"/>
       <c r="J46" s="10"/>
       <c r="K46" s="10"/>
-      <c r="L46" s="5"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="10"/>
+      <c r="Q46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5"/>
@@ -5508,7 +7286,12 @@
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
       <c r="K47" s="10"/>
-      <c r="L47" s="5"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="10"/>
+      <c r="Q47" s="10"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5"/>
@@ -5522,7 +7305,12 @@
       <c r="I48" s="10"/>
       <c r="J48" s="10"/>
       <c r="K48" s="10"/>
-      <c r="L48" s="5"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="10"/>
+      <c r="Q48" s="10"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5"/>
@@ -5536,7 +7324,12 @@
       <c r="I49" s="10"/>
       <c r="J49" s="10"/>
       <c r="K49" s="10"/>
-      <c r="L49" s="5"/>
+      <c r="L49" s="10"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="10"/>
+      <c r="Q49" s="10"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5"/>
@@ -5550,7 +7343,12 @@
       <c r="I50" s="10"/>
       <c r="J50" s="10"/>
       <c r="K50" s="10"/>
-      <c r="L50" s="5"/>
+      <c r="L50" s="10"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="10"/>
+      <c r="Q50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5"/>
@@ -5564,7 +7362,12 @@
       <c r="I51" s="10"/>
       <c r="J51" s="10"/>
       <c r="K51" s="10"/>
-      <c r="L51" s="5"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="10"/>
+      <c r="Q51" s="10"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5"/>
@@ -5578,7 +7381,12 @@
       <c r="I52" s="10"/>
       <c r="J52" s="10"/>
       <c r="K52" s="10"/>
-      <c r="L52" s="5"/>
+      <c r="L52" s="10"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="10"/>
+      <c r="Q52" s="10"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5"/>
@@ -5592,7 +7400,12 @@
       <c r="I53" s="10"/>
       <c r="J53" s="10"/>
       <c r="K53" s="10"/>
-      <c r="L53" s="5"/>
+      <c r="L53" s="10"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="10"/>
+      <c r="Q53" s="10"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5"/>
@@ -5606,7 +7419,12 @@
       <c r="I54" s="10"/>
       <c r="J54" s="10"/>
       <c r="K54" s="10"/>
-      <c r="L54" s="5"/>
+      <c r="L54" s="10"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="10"/>
+      <c r="Q54" s="10"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5"/>
@@ -5620,7 +7438,12 @@
       <c r="I55" s="10"/>
       <c r="J55" s="10"/>
       <c r="K55" s="10"/>
-      <c r="L55" s="5"/>
+      <c r="L55" s="10"/>
+      <c r="M55" s="10"/>
+      <c r="N55" s="5"/>
+      <c r="O55" s="5"/>
+      <c r="P55" s="10"/>
+      <c r="Q55" s="10"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5"/>
@@ -5634,7 +7457,12 @@
       <c r="I56" s="10"/>
       <c r="J56" s="10"/>
       <c r="K56" s="10"/>
-      <c r="L56" s="5"/>
+      <c r="L56" s="10"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="5"/>
+      <c r="O56" s="5"/>
+      <c r="P56" s="10"/>
+      <c r="Q56" s="10"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5"/>
@@ -5648,7 +7476,12 @@
       <c r="I57" s="10"/>
       <c r="J57" s="10"/>
       <c r="K57" s="10"/>
-      <c r="L57" s="5"/>
+      <c r="L57" s="10"/>
+      <c r="M57" s="10"/>
+      <c r="N57" s="5"/>
+      <c r="O57" s="5"/>
+      <c r="P57" s="10"/>
+      <c r="Q57" s="10"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5"/>
@@ -5662,7 +7495,12 @@
       <c r="I58" s="10"/>
       <c r="J58" s="10"/>
       <c r="K58" s="10"/>
-      <c r="L58" s="5"/>
+      <c r="L58" s="10"/>
+      <c r="M58" s="10"/>
+      <c r="N58" s="5"/>
+      <c r="O58" s="5"/>
+      <c r="P58" s="10"/>
+      <c r="Q58" s="10"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5"/>
@@ -5676,7 +7514,12 @@
       <c r="I59" s="10"/>
       <c r="J59" s="10"/>
       <c r="K59" s="10"/>
-      <c r="L59" s="5"/>
+      <c r="L59" s="10"/>
+      <c r="M59" s="10"/>
+      <c r="N59" s="5"/>
+      <c r="O59" s="5"/>
+      <c r="P59" s="10"/>
+      <c r="Q59" s="10"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5"/>
@@ -5690,7 +7533,12 @@
       <c r="I60" s="10"/>
       <c r="J60" s="10"/>
       <c r="K60" s="10"/>
-      <c r="L60" s="5"/>
+      <c r="L60" s="10"/>
+      <c r="M60" s="10"/>
+      <c r="N60" s="5"/>
+      <c r="O60" s="5"/>
+      <c r="P60" s="10"/>
+      <c r="Q60" s="10"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5"/>
@@ -5704,7 +7552,12 @@
       <c r="I61" s="10"/>
       <c r="J61" s="10"/>
       <c r="K61" s="10"/>
-      <c r="L61" s="5"/>
+      <c r="L61" s="10"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="5"/>
+      <c r="O61" s="5"/>
+      <c r="P61" s="10"/>
+      <c r="Q61" s="10"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5"/>
@@ -5718,7 +7571,12 @@
       <c r="I62" s="10"/>
       <c r="J62" s="10"/>
       <c r="K62" s="10"/>
-      <c r="L62" s="5"/>
+      <c r="L62" s="10"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="5"/>
+      <c r="O62" s="5"/>
+      <c r="P62" s="10"/>
+      <c r="Q62" s="10"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5"/>
@@ -5732,7 +7590,12 @@
       <c r="I63" s="10"/>
       <c r="J63" s="10"/>
       <c r="K63" s="10"/>
-      <c r="L63" s="5"/>
+      <c r="L63" s="10"/>
+      <c r="M63" s="10"/>
+      <c r="N63" s="5"/>
+      <c r="O63" s="5"/>
+      <c r="P63" s="10"/>
+      <c r="Q63" s="10"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5"/>
@@ -5746,7 +7609,12 @@
       <c r="I64" s="10"/>
       <c r="J64" s="10"/>
       <c r="K64" s="10"/>
-      <c r="L64" s="5"/>
+      <c r="L64" s="10"/>
+      <c r="M64" s="10"/>
+      <c r="N64" s="5"/>
+      <c r="O64" s="5"/>
+      <c r="P64" s="10"/>
+      <c r="Q64" s="10"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5"/>
@@ -5760,7 +7628,12 @@
       <c r="I65" s="10"/>
       <c r="J65" s="10"/>
       <c r="K65" s="10"/>
-      <c r="L65" s="5"/>
+      <c r="L65" s="10"/>
+      <c r="M65" s="10"/>
+      <c r="N65" s="5"/>
+      <c r="O65" s="5"/>
+      <c r="P65" s="10"/>
+      <c r="Q65" s="10"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5"/>
@@ -5774,7 +7647,12 @@
       <c r="I66" s="10"/>
       <c r="J66" s="10"/>
       <c r="K66" s="10"/>
-      <c r="L66" s="5"/>
+      <c r="L66" s="10"/>
+      <c r="M66" s="10"/>
+      <c r="N66" s="5"/>
+      <c r="O66" s="5"/>
+      <c r="P66" s="10"/>
+      <c r="Q66" s="10"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5"/>
@@ -5788,7 +7666,12 @@
       <c r="I67" s="10"/>
       <c r="J67" s="10"/>
       <c r="K67" s="10"/>
-      <c r="L67" s="5"/>
+      <c r="L67" s="10"/>
+      <c r="M67" s="10"/>
+      <c r="N67" s="5"/>
+      <c r="O67" s="5"/>
+      <c r="P67" s="10"/>
+      <c r="Q67" s="10"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5"/>
@@ -5802,7 +7685,12 @@
       <c r="I68" s="10"/>
       <c r="J68" s="10"/>
       <c r="K68" s="10"/>
-      <c r="L68" s="5"/>
+      <c r="L68" s="10"/>
+      <c r="M68" s="10"/>
+      <c r="N68" s="5"/>
+      <c r="O68" s="5"/>
+      <c r="P68" s="10"/>
+      <c r="Q68" s="10"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5"/>
@@ -5816,7 +7704,12 @@
       <c r="I69" s="10"/>
       <c r="J69" s="10"/>
       <c r="K69" s="10"/>
-      <c r="L69" s="5"/>
+      <c r="L69" s="10"/>
+      <c r="M69" s="10"/>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5"/>
+      <c r="P69" s="10"/>
+      <c r="Q69" s="10"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5"/>
@@ -5830,7 +7723,12 @@
       <c r="I70" s="10"/>
       <c r="J70" s="10"/>
       <c r="K70" s="10"/>
-      <c r="L70" s="5"/>
+      <c r="L70" s="10"/>
+      <c r="M70" s="10"/>
+      <c r="N70" s="5"/>
+      <c r="O70" s="5"/>
+      <c r="P70" s="10"/>
+      <c r="Q70" s="10"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5"/>
@@ -5844,7 +7742,12 @@
       <c r="I71" s="10"/>
       <c r="J71" s="10"/>
       <c r="K71" s="10"/>
-      <c r="L71" s="5"/>
+      <c r="L71" s="10"/>
+      <c r="M71" s="10"/>
+      <c r="N71" s="5"/>
+      <c r="O71" s="5"/>
+      <c r="P71" s="10"/>
+      <c r="Q71" s="10"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5"/>
@@ -5858,7 +7761,12 @@
       <c r="I72" s="10"/>
       <c r="J72" s="10"/>
       <c r="K72" s="10"/>
-      <c r="L72" s="5"/>
+      <c r="L72" s="10"/>
+      <c r="M72" s="10"/>
+      <c r="N72" s="5"/>
+      <c r="O72" s="5"/>
+      <c r="P72" s="10"/>
+      <c r="Q72" s="10"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5"/>
@@ -5872,7 +7780,12 @@
       <c r="I73" s="10"/>
       <c r="J73" s="10"/>
       <c r="K73" s="10"/>
-      <c r="L73" s="5"/>
+      <c r="L73" s="10"/>
+      <c r="M73" s="10"/>
+      <c r="N73" s="5"/>
+      <c r="O73" s="5"/>
+      <c r="P73" s="10"/>
+      <c r="Q73" s="10"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5"/>
@@ -5886,7 +7799,12 @@
       <c r="I74" s="10"/>
       <c r="J74" s="10"/>
       <c r="K74" s="10"/>
-      <c r="L74" s="5"/>
+      <c r="L74" s="10"/>
+      <c r="M74" s="10"/>
+      <c r="N74" s="5"/>
+      <c r="O74" s="5"/>
+      <c r="P74" s="10"/>
+      <c r="Q74" s="10"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5"/>
@@ -5900,7 +7818,12 @@
       <c r="I75" s="10"/>
       <c r="J75" s="10"/>
       <c r="K75" s="10"/>
-      <c r="L75" s="5"/>
+      <c r="L75" s="10"/>
+      <c r="M75" s="10"/>
+      <c r="N75" s="5"/>
+      <c r="O75" s="5"/>
+      <c r="P75" s="10"/>
+      <c r="Q75" s="10"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5"/>
@@ -5914,7 +7837,12 @@
       <c r="I76" s="10"/>
       <c r="J76" s="10"/>
       <c r="K76" s="10"/>
-      <c r="L76" s="5"/>
+      <c r="L76" s="10"/>
+      <c r="M76" s="10"/>
+      <c r="N76" s="5"/>
+      <c r="O76" s="5"/>
+      <c r="P76" s="10"/>
+      <c r="Q76" s="10"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5"/>
@@ -5928,7 +7856,12 @@
       <c r="I77" s="10"/>
       <c r="J77" s="10"/>
       <c r="K77" s="10"/>
-      <c r="L77" s="5"/>
+      <c r="L77" s="10"/>
+      <c r="M77" s="10"/>
+      <c r="N77" s="5"/>
+      <c r="O77" s="5"/>
+      <c r="P77" s="10"/>
+      <c r="Q77" s="10"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5"/>
@@ -5942,7 +7875,12 @@
       <c r="I78" s="10"/>
       <c r="J78" s="10"/>
       <c r="K78" s="10"/>
-      <c r="L78" s="5"/>
+      <c r="L78" s="10"/>
+      <c r="M78" s="10"/>
+      <c r="N78" s="5"/>
+      <c r="O78" s="5"/>
+      <c r="P78" s="10"/>
+      <c r="Q78" s="10"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5"/>
@@ -5956,7 +7894,12 @@
       <c r="I79" s="10"/>
       <c r="J79" s="10"/>
       <c r="K79" s="10"/>
-      <c r="L79" s="5"/>
+      <c r="L79" s="10"/>
+      <c r="M79" s="10"/>
+      <c r="N79" s="5"/>
+      <c r="O79" s="5"/>
+      <c r="P79" s="10"/>
+      <c r="Q79" s="10"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5"/>
@@ -5970,7 +7913,12 @@
       <c r="I80" s="10"/>
       <c r="J80" s="10"/>
       <c r="K80" s="10"/>
-      <c r="L80" s="5"/>
+      <c r="L80" s="10"/>
+      <c r="M80" s="10"/>
+      <c r="N80" s="5"/>
+      <c r="O80" s="5"/>
+      <c r="P80" s="10"/>
+      <c r="Q80" s="10"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5"/>
@@ -5984,7 +7932,12 @@
       <c r="I81" s="10"/>
       <c r="J81" s="10"/>
       <c r="K81" s="10"/>
-      <c r="L81" s="5"/>
+      <c r="L81" s="10"/>
+      <c r="M81" s="10"/>
+      <c r="N81" s="5"/>
+      <c r="O81" s="5"/>
+      <c r="P81" s="10"/>
+      <c r="Q81" s="10"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5"/>
@@ -5998,7 +7951,12 @@
       <c r="I82" s="10"/>
       <c r="J82" s="10"/>
       <c r="K82" s="10"/>
-      <c r="L82" s="5"/>
+      <c r="L82" s="10"/>
+      <c r="M82" s="10"/>
+      <c r="N82" s="5"/>
+      <c r="O82" s="5"/>
+      <c r="P82" s="10"/>
+      <c r="Q82" s="10"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5"/>
@@ -6012,7 +7970,12 @@
       <c r="I83" s="10"/>
       <c r="J83" s="10"/>
       <c r="K83" s="10"/>
-      <c r="L83" s="5"/>
+      <c r="L83" s="10"/>
+      <c r="M83" s="10"/>
+      <c r="N83" s="5"/>
+      <c r="O83" s="5"/>
+      <c r="P83" s="10"/>
+      <c r="Q83" s="10"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5"/>
@@ -6026,10 +7989,15 @@
       <c r="I84" s="10"/>
       <c r="J84" s="10"/>
       <c r="K84" s="10"/>
-      <c r="L84" s="5"/>
+      <c r="L84" s="10"/>
+      <c r="M84" s="10"/>
+      <c r="N84" s="5"/>
+      <c r="O84" s="5"/>
+      <c r="P84" s="10"/>
+      <c r="Q84" s="10"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A5:L84">
+  <conditionalFormatting sqref="A5:Q84">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$A5&lt;&gt;""</formula>
     </cfRule>
@@ -6039,7 +8007,7 @@
       <formula>$C5="P. Principal"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="8">
+  <dataValidations count="12">
     <dataValidation allowBlank="true" error="Solo un número de 1 a 20." errorStyle="stop" errorTitle="Series" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E5:E84" type="whole">
       <formula1>1</formula1>
       <formula2>20</formula2>
@@ -6064,12 +8032,28 @@
       <formula1>"Sí"</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation allowBlank="true" error="Minutos del aeróbico (0,5 = 30 s)." errorStyle="stop" errorTitle="Minutos" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L5:L84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>600</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" errorTitle="RPE pre" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P5:P84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" errorTitle="RPE post" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q5:Q84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable (Lunes … Domingo)." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A5:A84" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Elige un bloque del desplegable." errorStyle="stop" errorTitle="Bloque" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C5:C84" type="list">
-      <formula1>"Activación,P. Principal,Accesorios,Vuelta a la calma"</formula1>
+      <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M5:M84" type="list">
+      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -6088,7 +8072,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:Q84"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
@@ -6100,12 +8084,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="0" width="8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B1" s="11" t="n">
         <f aca="false">'Semana 4'!B1+7</f>
@@ -6118,46 +8106,61 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B2" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6172,7 +8175,12 @@
       <c r="I5" s="10"/>
       <c r="J5" s="10"/>
       <c r="K5" s="10"/>
-      <c r="L5" s="5"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
@@ -6186,7 +8194,12 @@
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
-      <c r="L6" s="5"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
@@ -6200,7 +8213,12 @@
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
-      <c r="L7" s="5"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
@@ -6214,7 +8232,12 @@
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
-      <c r="L8" s="5"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
@@ -6228,7 +8251,12 @@
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
-      <c r="L9" s="5"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
@@ -6242,7 +8270,12 @@
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
-      <c r="L10" s="5"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
@@ -6256,7 +8289,12 @@
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
-      <c r="L11" s="5"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
@@ -6270,7 +8308,12 @@
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
-      <c r="L12" s="5"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
@@ -6284,7 +8327,12 @@
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
-      <c r="L13" s="5"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
@@ -6298,7 +8346,12 @@
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
-      <c r="L14" s="5"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
@@ -6312,7 +8365,12 @@
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
-      <c r="L15" s="5"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5"/>
@@ -6326,7 +8384,12 @@
       <c r="I16" s="10"/>
       <c r="J16" s="10"/>
       <c r="K16" s="10"/>
-      <c r="L16" s="5"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5"/>
@@ -6340,7 +8403,12 @@
       <c r="I17" s="10"/>
       <c r="J17" s="10"/>
       <c r="K17" s="10"/>
-      <c r="L17" s="5"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5"/>
@@ -6354,7 +8422,12 @@
       <c r="I18" s="10"/>
       <c r="J18" s="10"/>
       <c r="K18" s="10"/>
-      <c r="L18" s="5"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5"/>
@@ -6368,7 +8441,12 @@
       <c r="I19" s="10"/>
       <c r="J19" s="10"/>
       <c r="K19" s="10"/>
-      <c r="L19" s="5"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5"/>
@@ -6382,7 +8460,12 @@
       <c r="I20" s="10"/>
       <c r="J20" s="10"/>
       <c r="K20" s="10"/>
-      <c r="L20" s="5"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5"/>
@@ -6396,7 +8479,12 @@
       <c r="I21" s="10"/>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
-      <c r="L21" s="5"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5"/>
@@ -6410,7 +8498,12 @@
       <c r="I22" s="10"/>
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
-      <c r="L22" s="5"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5"/>
@@ -6424,7 +8517,12 @@
       <c r="I23" s="10"/>
       <c r="J23" s="10"/>
       <c r="K23" s="10"/>
-      <c r="L23" s="5"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5"/>
@@ -6438,7 +8536,12 @@
       <c r="I24" s="10"/>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
-      <c r="L24" s="5"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5"/>
@@ -6452,7 +8555,12 @@
       <c r="I25" s="10"/>
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
-      <c r="L25" s="5"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5"/>
@@ -6466,7 +8574,12 @@
       <c r="I26" s="10"/>
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
-      <c r="L26" s="5"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5"/>
@@ -6480,7 +8593,12 @@
       <c r="I27" s="10"/>
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
-      <c r="L27" s="5"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5"/>
@@ -6494,7 +8612,12 @@
       <c r="I28" s="10"/>
       <c r="J28" s="10"/>
       <c r="K28" s="10"/>
-      <c r="L28" s="5"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5"/>
@@ -6508,7 +8631,12 @@
       <c r="I29" s="10"/>
       <c r="J29" s="10"/>
       <c r="K29" s="10"/>
-      <c r="L29" s="5"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5"/>
@@ -6522,7 +8650,12 @@
       <c r="I30" s="10"/>
       <c r="J30" s="10"/>
       <c r="K30" s="10"/>
-      <c r="L30" s="5"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="10"/>
+      <c r="Q30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5"/>
@@ -6536,7 +8669,12 @@
       <c r="I31" s="10"/>
       <c r="J31" s="10"/>
       <c r="K31" s="10"/>
-      <c r="L31" s="5"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="10"/>
+      <c r="Q31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5"/>
@@ -6550,7 +8688,12 @@
       <c r="I32" s="10"/>
       <c r="J32" s="10"/>
       <c r="K32" s="10"/>
-      <c r="L32" s="5"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="10"/>
+      <c r="Q32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5"/>
@@ -6564,7 +8707,12 @@
       <c r="I33" s="10"/>
       <c r="J33" s="10"/>
       <c r="K33" s="10"/>
-      <c r="L33" s="5"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="10"/>
+      <c r="Q33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5"/>
@@ -6578,7 +8726,12 @@
       <c r="I34" s="10"/>
       <c r="J34" s="10"/>
       <c r="K34" s="10"/>
-      <c r="L34" s="5"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5"/>
@@ -6592,7 +8745,12 @@
       <c r="I35" s="10"/>
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
-      <c r="L35" s="5"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5"/>
@@ -6606,7 +8764,12 @@
       <c r="I36" s="10"/>
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
-      <c r="L36" s="5"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="10"/>
+      <c r="Q36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5"/>
@@ -6620,7 +8783,12 @@
       <c r="I37" s="10"/>
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
-      <c r="L37" s="5"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5"/>
@@ -6634,7 +8802,12 @@
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
-      <c r="L38" s="5"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5"/>
@@ -6648,7 +8821,12 @@
       <c r="I39" s="10"/>
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
-      <c r="L39" s="5"/>
+      <c r="L39" s="10"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5"/>
@@ -6662,7 +8840,12 @@
       <c r="I40" s="10"/>
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
-      <c r="L40" s="5"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="10"/>
+      <c r="Q40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5"/>
@@ -6676,7 +8859,12 @@
       <c r="I41" s="10"/>
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
-      <c r="L41" s="5"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5"/>
@@ -6690,7 +8878,12 @@
       <c r="I42" s="10"/>
       <c r="J42" s="10"/>
       <c r="K42" s="10"/>
-      <c r="L42" s="5"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="10"/>
+      <c r="Q42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5"/>
@@ -6704,7 +8897,12 @@
       <c r="I43" s="10"/>
       <c r="J43" s="10"/>
       <c r="K43" s="10"/>
-      <c r="L43" s="5"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="10"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5"/>
@@ -6718,7 +8916,12 @@
       <c r="I44" s="10"/>
       <c r="J44" s="10"/>
       <c r="K44" s="10"/>
-      <c r="L44" s="5"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="10"/>
+      <c r="Q44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5"/>
@@ -6732,7 +8935,12 @@
       <c r="I45" s="10"/>
       <c r="J45" s="10"/>
       <c r="K45" s="10"/>
-      <c r="L45" s="5"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="10"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5"/>
@@ -6746,7 +8954,12 @@
       <c r="I46" s="10"/>
       <c r="J46" s="10"/>
       <c r="K46" s="10"/>
-      <c r="L46" s="5"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="10"/>
+      <c r="Q46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5"/>
@@ -6760,7 +8973,12 @@
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
       <c r="K47" s="10"/>
-      <c r="L47" s="5"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="10"/>
+      <c r="Q47" s="10"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5"/>
@@ -6774,7 +8992,12 @@
       <c r="I48" s="10"/>
       <c r="J48" s="10"/>
       <c r="K48" s="10"/>
-      <c r="L48" s="5"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="10"/>
+      <c r="Q48" s="10"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5"/>
@@ -6788,7 +9011,12 @@
       <c r="I49" s="10"/>
       <c r="J49" s="10"/>
       <c r="K49" s="10"/>
-      <c r="L49" s="5"/>
+      <c r="L49" s="10"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="10"/>
+      <c r="Q49" s="10"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5"/>
@@ -6802,7 +9030,12 @@
       <c r="I50" s="10"/>
       <c r="J50" s="10"/>
       <c r="K50" s="10"/>
-      <c r="L50" s="5"/>
+      <c r="L50" s="10"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="10"/>
+      <c r="Q50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5"/>
@@ -6816,7 +9049,12 @@
       <c r="I51" s="10"/>
       <c r="J51" s="10"/>
       <c r="K51" s="10"/>
-      <c r="L51" s="5"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="10"/>
+      <c r="Q51" s="10"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5"/>
@@ -6830,7 +9068,12 @@
       <c r="I52" s="10"/>
       <c r="J52" s="10"/>
       <c r="K52" s="10"/>
-      <c r="L52" s="5"/>
+      <c r="L52" s="10"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="10"/>
+      <c r="Q52" s="10"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5"/>
@@ -6844,7 +9087,12 @@
       <c r="I53" s="10"/>
       <c r="J53" s="10"/>
       <c r="K53" s="10"/>
-      <c r="L53" s="5"/>
+      <c r="L53" s="10"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="10"/>
+      <c r="Q53" s="10"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5"/>
@@ -6858,7 +9106,12 @@
       <c r="I54" s="10"/>
       <c r="J54" s="10"/>
       <c r="K54" s="10"/>
-      <c r="L54" s="5"/>
+      <c r="L54" s="10"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="10"/>
+      <c r="Q54" s="10"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5"/>
@@ -6872,7 +9125,12 @@
       <c r="I55" s="10"/>
       <c r="J55" s="10"/>
       <c r="K55" s="10"/>
-      <c r="L55" s="5"/>
+      <c r="L55" s="10"/>
+      <c r="M55" s="10"/>
+      <c r="N55" s="5"/>
+      <c r="O55" s="5"/>
+      <c r="P55" s="10"/>
+      <c r="Q55" s="10"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5"/>
@@ -6886,7 +9144,12 @@
       <c r="I56" s="10"/>
       <c r="J56" s="10"/>
       <c r="K56" s="10"/>
-      <c r="L56" s="5"/>
+      <c r="L56" s="10"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="5"/>
+      <c r="O56" s="5"/>
+      <c r="P56" s="10"/>
+      <c r="Q56" s="10"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5"/>
@@ -6900,7 +9163,12 @@
       <c r="I57" s="10"/>
       <c r="J57" s="10"/>
       <c r="K57" s="10"/>
-      <c r="L57" s="5"/>
+      <c r="L57" s="10"/>
+      <c r="M57" s="10"/>
+      <c r="N57" s="5"/>
+      <c r="O57" s="5"/>
+      <c r="P57" s="10"/>
+      <c r="Q57" s="10"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5"/>
@@ -6914,7 +9182,12 @@
       <c r="I58" s="10"/>
       <c r="J58" s="10"/>
       <c r="K58" s="10"/>
-      <c r="L58" s="5"/>
+      <c r="L58" s="10"/>
+      <c r="M58" s="10"/>
+      <c r="N58" s="5"/>
+      <c r="O58" s="5"/>
+      <c r="P58" s="10"/>
+      <c r="Q58" s="10"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5"/>
@@ -6928,7 +9201,12 @@
       <c r="I59" s="10"/>
       <c r="J59" s="10"/>
       <c r="K59" s="10"/>
-      <c r="L59" s="5"/>
+      <c r="L59" s="10"/>
+      <c r="M59" s="10"/>
+      <c r="N59" s="5"/>
+      <c r="O59" s="5"/>
+      <c r="P59" s="10"/>
+      <c r="Q59" s="10"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5"/>
@@ -6942,7 +9220,12 @@
       <c r="I60" s="10"/>
       <c r="J60" s="10"/>
       <c r="K60" s="10"/>
-      <c r="L60" s="5"/>
+      <c r="L60" s="10"/>
+      <c r="M60" s="10"/>
+      <c r="N60" s="5"/>
+      <c r="O60" s="5"/>
+      <c r="P60" s="10"/>
+      <c r="Q60" s="10"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5"/>
@@ -6956,7 +9239,12 @@
       <c r="I61" s="10"/>
       <c r="J61" s="10"/>
       <c r="K61" s="10"/>
-      <c r="L61" s="5"/>
+      <c r="L61" s="10"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="5"/>
+      <c r="O61" s="5"/>
+      <c r="P61" s="10"/>
+      <c r="Q61" s="10"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5"/>
@@ -6970,7 +9258,12 @@
       <c r="I62" s="10"/>
       <c r="J62" s="10"/>
       <c r="K62" s="10"/>
-      <c r="L62" s="5"/>
+      <c r="L62" s="10"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="5"/>
+      <c r="O62" s="5"/>
+      <c r="P62" s="10"/>
+      <c r="Q62" s="10"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5"/>
@@ -6984,7 +9277,12 @@
       <c r="I63" s="10"/>
       <c r="J63" s="10"/>
       <c r="K63" s="10"/>
-      <c r="L63" s="5"/>
+      <c r="L63" s="10"/>
+      <c r="M63" s="10"/>
+      <c r="N63" s="5"/>
+      <c r="O63" s="5"/>
+      <c r="P63" s="10"/>
+      <c r="Q63" s="10"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5"/>
@@ -6998,7 +9296,12 @@
       <c r="I64" s="10"/>
       <c r="J64" s="10"/>
       <c r="K64" s="10"/>
-      <c r="L64" s="5"/>
+      <c r="L64" s="10"/>
+      <c r="M64" s="10"/>
+      <c r="N64" s="5"/>
+      <c r="O64" s="5"/>
+      <c r="P64" s="10"/>
+      <c r="Q64" s="10"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5"/>
@@ -7012,7 +9315,12 @@
       <c r="I65" s="10"/>
       <c r="J65" s="10"/>
       <c r="K65" s="10"/>
-      <c r="L65" s="5"/>
+      <c r="L65" s="10"/>
+      <c r="M65" s="10"/>
+      <c r="N65" s="5"/>
+      <c r="O65" s="5"/>
+      <c r="P65" s="10"/>
+      <c r="Q65" s="10"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5"/>
@@ -7026,7 +9334,12 @@
       <c r="I66" s="10"/>
       <c r="J66" s="10"/>
       <c r="K66" s="10"/>
-      <c r="L66" s="5"/>
+      <c r="L66" s="10"/>
+      <c r="M66" s="10"/>
+      <c r="N66" s="5"/>
+      <c r="O66" s="5"/>
+      <c r="P66" s="10"/>
+      <c r="Q66" s="10"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5"/>
@@ -7040,7 +9353,12 @@
       <c r="I67" s="10"/>
       <c r="J67" s="10"/>
       <c r="K67" s="10"/>
-      <c r="L67" s="5"/>
+      <c r="L67" s="10"/>
+      <c r="M67" s="10"/>
+      <c r="N67" s="5"/>
+      <c r="O67" s="5"/>
+      <c r="P67" s="10"/>
+      <c r="Q67" s="10"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5"/>
@@ -7054,7 +9372,12 @@
       <c r="I68" s="10"/>
       <c r="J68" s="10"/>
       <c r="K68" s="10"/>
-      <c r="L68" s="5"/>
+      <c r="L68" s="10"/>
+      <c r="M68" s="10"/>
+      <c r="N68" s="5"/>
+      <c r="O68" s="5"/>
+      <c r="P68" s="10"/>
+      <c r="Q68" s="10"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5"/>
@@ -7068,7 +9391,12 @@
       <c r="I69" s="10"/>
       <c r="J69" s="10"/>
       <c r="K69" s="10"/>
-      <c r="L69" s="5"/>
+      <c r="L69" s="10"/>
+      <c r="M69" s="10"/>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5"/>
+      <c r="P69" s="10"/>
+      <c r="Q69" s="10"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5"/>
@@ -7082,7 +9410,12 @@
       <c r="I70" s="10"/>
       <c r="J70" s="10"/>
       <c r="K70" s="10"/>
-      <c r="L70" s="5"/>
+      <c r="L70" s="10"/>
+      <c r="M70" s="10"/>
+      <c r="N70" s="5"/>
+      <c r="O70" s="5"/>
+      <c r="P70" s="10"/>
+      <c r="Q70" s="10"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5"/>
@@ -7096,7 +9429,12 @@
       <c r="I71" s="10"/>
       <c r="J71" s="10"/>
       <c r="K71" s="10"/>
-      <c r="L71" s="5"/>
+      <c r="L71" s="10"/>
+      <c r="M71" s="10"/>
+      <c r="N71" s="5"/>
+      <c r="O71" s="5"/>
+      <c r="P71" s="10"/>
+      <c r="Q71" s="10"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5"/>
@@ -7110,7 +9448,12 @@
       <c r="I72" s="10"/>
       <c r="J72" s="10"/>
       <c r="K72" s="10"/>
-      <c r="L72" s="5"/>
+      <c r="L72" s="10"/>
+      <c r="M72" s="10"/>
+      <c r="N72" s="5"/>
+      <c r="O72" s="5"/>
+      <c r="P72" s="10"/>
+      <c r="Q72" s="10"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5"/>
@@ -7124,7 +9467,12 @@
       <c r="I73" s="10"/>
       <c r="J73" s="10"/>
       <c r="K73" s="10"/>
-      <c r="L73" s="5"/>
+      <c r="L73" s="10"/>
+      <c r="M73" s="10"/>
+      <c r="N73" s="5"/>
+      <c r="O73" s="5"/>
+      <c r="P73" s="10"/>
+      <c r="Q73" s="10"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5"/>
@@ -7138,7 +9486,12 @@
       <c r="I74" s="10"/>
       <c r="J74" s="10"/>
       <c r="K74" s="10"/>
-      <c r="L74" s="5"/>
+      <c r="L74" s="10"/>
+      <c r="M74" s="10"/>
+      <c r="N74" s="5"/>
+      <c r="O74" s="5"/>
+      <c r="P74" s="10"/>
+      <c r="Q74" s="10"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5"/>
@@ -7152,7 +9505,12 @@
       <c r="I75" s="10"/>
       <c r="J75" s="10"/>
       <c r="K75" s="10"/>
-      <c r="L75" s="5"/>
+      <c r="L75" s="10"/>
+      <c r="M75" s="10"/>
+      <c r="N75" s="5"/>
+      <c r="O75" s="5"/>
+      <c r="P75" s="10"/>
+      <c r="Q75" s="10"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5"/>
@@ -7166,7 +9524,12 @@
       <c r="I76" s="10"/>
       <c r="J76" s="10"/>
       <c r="K76" s="10"/>
-      <c r="L76" s="5"/>
+      <c r="L76" s="10"/>
+      <c r="M76" s="10"/>
+      <c r="N76" s="5"/>
+      <c r="O76" s="5"/>
+      <c r="P76" s="10"/>
+      <c r="Q76" s="10"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5"/>
@@ -7180,7 +9543,12 @@
       <c r="I77" s="10"/>
       <c r="J77" s="10"/>
       <c r="K77" s="10"/>
-      <c r="L77" s="5"/>
+      <c r="L77" s="10"/>
+      <c r="M77" s="10"/>
+      <c r="N77" s="5"/>
+      <c r="O77" s="5"/>
+      <c r="P77" s="10"/>
+      <c r="Q77" s="10"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5"/>
@@ -7194,7 +9562,12 @@
       <c r="I78" s="10"/>
       <c r="J78" s="10"/>
       <c r="K78" s="10"/>
-      <c r="L78" s="5"/>
+      <c r="L78" s="10"/>
+      <c r="M78" s="10"/>
+      <c r="N78" s="5"/>
+      <c r="O78" s="5"/>
+      <c r="P78" s="10"/>
+      <c r="Q78" s="10"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5"/>
@@ -7208,7 +9581,12 @@
       <c r="I79" s="10"/>
       <c r="J79" s="10"/>
       <c r="K79" s="10"/>
-      <c r="L79" s="5"/>
+      <c r="L79" s="10"/>
+      <c r="M79" s="10"/>
+      <c r="N79" s="5"/>
+      <c r="O79" s="5"/>
+      <c r="P79" s="10"/>
+      <c r="Q79" s="10"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5"/>
@@ -7222,7 +9600,12 @@
       <c r="I80" s="10"/>
       <c r="J80" s="10"/>
       <c r="K80" s="10"/>
-      <c r="L80" s="5"/>
+      <c r="L80" s="10"/>
+      <c r="M80" s="10"/>
+      <c r="N80" s="5"/>
+      <c r="O80" s="5"/>
+      <c r="P80" s="10"/>
+      <c r="Q80" s="10"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5"/>
@@ -7236,7 +9619,12 @@
       <c r="I81" s="10"/>
       <c r="J81" s="10"/>
       <c r="K81" s="10"/>
-      <c r="L81" s="5"/>
+      <c r="L81" s="10"/>
+      <c r="M81" s="10"/>
+      <c r="N81" s="5"/>
+      <c r="O81" s="5"/>
+      <c r="P81" s="10"/>
+      <c r="Q81" s="10"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5"/>
@@ -7250,7 +9638,12 @@
       <c r="I82" s="10"/>
       <c r="J82" s="10"/>
       <c r="K82" s="10"/>
-      <c r="L82" s="5"/>
+      <c r="L82" s="10"/>
+      <c r="M82" s="10"/>
+      <c r="N82" s="5"/>
+      <c r="O82" s="5"/>
+      <c r="P82" s="10"/>
+      <c r="Q82" s="10"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5"/>
@@ -7264,7 +9657,12 @@
       <c r="I83" s="10"/>
       <c r="J83" s="10"/>
       <c r="K83" s="10"/>
-      <c r="L83" s="5"/>
+      <c r="L83" s="10"/>
+      <c r="M83" s="10"/>
+      <c r="N83" s="5"/>
+      <c r="O83" s="5"/>
+      <c r="P83" s="10"/>
+      <c r="Q83" s="10"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5"/>
@@ -7278,10 +9676,15 @@
       <c r="I84" s="10"/>
       <c r="J84" s="10"/>
       <c r="K84" s="10"/>
-      <c r="L84" s="5"/>
+      <c r="L84" s="10"/>
+      <c r="M84" s="10"/>
+      <c r="N84" s="5"/>
+      <c r="O84" s="5"/>
+      <c r="P84" s="10"/>
+      <c r="Q84" s="10"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A5:L84">
+  <conditionalFormatting sqref="A5:Q84">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$A5&lt;&gt;""</formula>
     </cfRule>
@@ -7291,7 +9694,7 @@
       <formula>$C5="P. Principal"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="8">
+  <dataValidations count="12">
     <dataValidation allowBlank="true" error="Solo un número de 1 a 20." errorStyle="stop" errorTitle="Series" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E5:E84" type="whole">
       <formula1>1</formula1>
       <formula2>20</formula2>
@@ -7316,12 +9719,28 @@
       <formula1>"Sí"</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation allowBlank="true" error="Minutos del aeróbico (0,5 = 30 s)." errorStyle="stop" errorTitle="Minutos" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L5:L84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>600</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" errorTitle="RPE pre" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P5:P84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" errorTitle="RPE post" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q5:Q84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable (Lunes … Domingo)." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A5:A84" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Elige un bloque del desplegable." errorStyle="stop" errorTitle="Bloque" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C5:C84" type="list">
-      <formula1>"Activación,P. Principal,Accesorios,Vuelta a la calma"</formula1>
+      <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M5:M84" type="list">
+      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>

--- a/plantillas/PLANTILLA_CLIENTE.xlsx
+++ b/plantillas/PLANTILLA_CLIENTE.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="46">
   <si>
     <t xml:space="preserve">Cómo se rellena esta plantilla</t>
   </si>
@@ -82,7 +82,7 @@
     <t xml:space="preserve">10. Peso (kg): solo el número (17,5). Si hace falta texto («por lado», «poner lastre»), va en Observaciones.</t>
   </si>
   <si>
-    <t xml:space="preserve">11. Aeróbico (al final de la sesión): Bloque «Aeróbico», Ejercicio = Carrera, Bicicleta…, y Minutos + Zona o Intervalos («10 Z2, 3 Z4, 10 Z2»). Una fila por sesión.</t>
+    <t xml:space="preserve">11. Aeróbico (al final de la sesión): Bloque «Aeróbico», Ejercicio = Carrera, Bicicleta…, y en Observaciones el tiempo y la zona: «20 min Z2» o, por intervalos, «10 Z2, 3 Z4, 10 Z2». Una fila por sesión.</t>
   </si>
   <si>
     <t xml:space="preserve">12. No cambies los títulos de las tablas ni la celda «SEMANA DEL». Puedes añadir más pestañas (ANUAL, RM…): se ignoran.</t>
@@ -121,15 +121,6 @@
     <t xml:space="preserve">Pliometría</t>
   </si>
   <si>
-    <t xml:space="preserve">Minutos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zona</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intervalos</t>
-  </si>
-  <si>
     <t xml:space="preserve">Observaciones</t>
   </si>
   <si>
@@ -166,7 +157,7 @@
     <t xml:space="preserve">Bicicleta</t>
   </si>
   <si>
-    <t xml:space="preserve">Z2</t>
+    <t xml:space="preserve">15 min Z2</t>
   </si>
   <si>
     <t xml:space="preserve">SEMANA DEL</t>
@@ -184,10 +175,7 @@
     <t xml:space="preserve">Nombre:</t>
   </si>
   <si>
-    <t xml:space="preserve">RPE pre:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPE post:</t>
+    <t xml:space="preserve">RPE pre / post:</t>
   </si>
   <si>
     <t xml:space="preserve">SESIÓN 2</t>
@@ -263,7 +251,7 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="13"/>
+      <sz val="12"/>
       <color rgb="FF1F4E79"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -309,15 +297,15 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF1B2A38"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF1B2A38"/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -446,7 +434,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -527,12 +515,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -833,20 +825,18 @@
     <tabColor rgb="FF1F4E79"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -867,9 +857,6 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
@@ -884,9 +871,6 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
@@ -901,9 +885,6 @@
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
@@ -918,9 +899,6 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
@@ -935,9 +913,6 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
@@ -952,9 +927,6 @@
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
@@ -969,9 +941,6 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
@@ -986,9 +955,6 @@
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
@@ -1003,9 +969,6 @@
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
@@ -1020,9 +983,6 @@
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
@@ -1037,9 +997,6 @@
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
@@ -1054,9 +1011,6 @@
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
@@ -1071,9 +1025,6 @@
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
@@ -1111,22 +1062,13 @@
       <c r="J18" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K18" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L18" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M18" s="5" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>2</v>
@@ -1139,17 +1081,14 @@
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="9"/>
+      <c r="J19" s="9"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C20" s="12" t="n">
         <v>3</v>
@@ -1158,7 +1097,7 @@
         <v>8</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>24</v>
@@ -1168,15 +1107,12 @@
       </c>
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="13"/>
+      <c r="J20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6"/>
       <c r="B21" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>3</v>
@@ -1185,25 +1121,22 @@
         <v>8</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F21" s="8" t="n">
         <v>10</v>
       </c>
       <c r="G21" s="8"/>
       <c r="H21" s="8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="9"/>
+      <c r="J21" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10"/>
       <c r="B22" s="11" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C22" s="12" t="n">
         <v>3</v>
@@ -1216,19 +1149,16 @@
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
       <c r="I22" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="13"/>
+        <v>32</v>
+      </c>
+      <c r="J22" s="13"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -1237,30 +1167,25 @@
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
-      <c r="J23" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="K23" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="L23" s="7"/>
-      <c r="M23" s="9"/>
+      <c r="J23" s="9" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="A5:M5"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="A9:M9"/>
-    <mergeCell ref="A10:M10"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A12:M12"/>
-    <mergeCell ref="A13:M13"/>
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:J15"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1278,25 +1203,23 @@
     <tabColor rgb="FF2E8B6E"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B1" s="15" t="n">
         <v>46328</v>
@@ -1306,7 +1229,7 @@
         <v>al 08/11</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
@@ -1314,28 +1237,23 @@
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F3" s="21"/>
       <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
+      <c r="H3" s="22" t="s">
+        <v>42</v>
+      </c>
       <c r="I3" s="21"/>
-      <c r="J3" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="K3" s="21"/>
-      <c r="L3" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="M3" s="21"/>
+      <c r="J3" s="21"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
@@ -1367,15 +1285,6 @@
       </c>
       <c r="J4" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1388,10 +1297,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="9"/>
+      <c r="J5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10"/>
@@ -1403,10 +1309,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="13"/>
+      <c r="J6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6"/>
@@ -1418,10 +1321,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="9"/>
+      <c r="J7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10"/>
@@ -1433,10 +1333,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="13"/>
+      <c r="J8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6"/>
@@ -1448,10 +1345,7 @@
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="9"/>
+      <c r="J9" s="9"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10"/>
@@ -1463,10 +1357,7 @@
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="13"/>
+      <c r="J10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6"/>
@@ -1478,10 +1369,7 @@
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="9"/>
+      <c r="J11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10"/>
@@ -1493,10 +1381,7 @@
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="13"/>
+      <c r="J12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6"/>
@@ -1508,10 +1393,7 @@
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="9"/>
+      <c r="J13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10"/>
@@ -1523,10 +1405,7 @@
       <c r="G14" s="12"/>
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="13"/>
+      <c r="J14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6"/>
@@ -1538,10 +1417,7 @@
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="9"/>
+      <c r="J15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10"/>
@@ -1553,10 +1429,7 @@
       <c r="G16" s="12"/>
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="13"/>
+      <c r="J16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6"/>
@@ -1568,10 +1441,7 @@
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="9"/>
+      <c r="J17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10"/>
@@ -1583,10 +1453,7 @@
       <c r="G18" s="12"/>
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="13"/>
+      <c r="J18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6"/>
@@ -1598,35 +1465,27 @@
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="9"/>
+      <c r="J19" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C22" s="21"/>
       <c r="D22" s="21"/>
       <c r="E22" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F22" s="21"/>
       <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
+      <c r="H22" s="22" t="s">
+        <v>42</v>
+      </c>
       <c r="I22" s="21"/>
-      <c r="J22" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="K22" s="21"/>
-      <c r="L22" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="M22" s="21"/>
+      <c r="J22" s="21"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
@@ -1658,15 +1517,6 @@
       </c>
       <c r="J23" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1679,10 +1529,7 @@
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="9"/>
+      <c r="J24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10"/>
@@ -1694,10 +1541,7 @@
       <c r="G25" s="12"/>
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="13"/>
+      <c r="J25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6"/>
@@ -1709,10 +1553,7 @@
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="9"/>
+      <c r="J26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10"/>
@@ -1724,10 +1565,7 @@
       <c r="G27" s="12"/>
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="13"/>
+      <c r="J27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6"/>
@@ -1739,10 +1577,7 @@
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="9"/>
+      <c r="J28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10"/>
@@ -1754,10 +1589,7 @@
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="13"/>
+      <c r="J29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6"/>
@@ -1769,10 +1601,7 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="9"/>
+      <c r="J30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10"/>
@@ -1784,10 +1613,7 @@
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="13"/>
+      <c r="J31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6"/>
@@ -1799,10 +1625,7 @@
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="9"/>
+      <c r="J32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10"/>
@@ -1814,10 +1637,7 @@
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="13"/>
+      <c r="J33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6"/>
@@ -1829,10 +1649,7 @@
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="9"/>
+      <c r="J34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10"/>
@@ -1844,10 +1661,7 @@
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="13"/>
+      <c r="J35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6"/>
@@ -1859,10 +1673,7 @@
       <c r="G36" s="8"/>
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="9"/>
+      <c r="J36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10"/>
@@ -1874,10 +1685,7 @@
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
       <c r="I37" s="12"/>
-      <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="13"/>
+      <c r="J37" s="13"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6"/>
@@ -1889,35 +1697,27 @@
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="9"/>
+      <c r="J38" s="9"/>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C41" s="21"/>
       <c r="D41" s="21"/>
       <c r="E41" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F41" s="21"/>
       <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
+      <c r="H41" s="22" t="s">
+        <v>42</v>
+      </c>
       <c r="I41" s="21"/>
-      <c r="J41" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="K41" s="21"/>
-      <c r="L41" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="M41" s="21"/>
+      <c r="J41" s="21"/>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
@@ -1949,15 +1749,6 @@
       </c>
       <c r="J42" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="K42" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L42" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1970,10 +1761,7 @@
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="7"/>
-      <c r="M43" s="9"/>
+      <c r="J43" s="9"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10"/>
@@ -1985,10 +1773,7 @@
       <c r="G44" s="12"/>
       <c r="H44" s="12"/>
       <c r="I44" s="12"/>
-      <c r="J44" s="12"/>
-      <c r="K44" s="12"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="13"/>
+      <c r="J44" s="13"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6"/>
@@ -2000,10 +1785,7 @@
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
-      <c r="L45" s="7"/>
-      <c r="M45" s="9"/>
+      <c r="J45" s="9"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10"/>
@@ -2015,10 +1797,7 @@
       <c r="G46" s="12"/>
       <c r="H46" s="12"/>
       <c r="I46" s="12"/>
-      <c r="J46" s="12"/>
-      <c r="K46" s="12"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="13"/>
+      <c r="J46" s="13"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6"/>
@@ -2030,10 +1809,7 @@
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="7"/>
-      <c r="M47" s="9"/>
+      <c r="J47" s="9"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10"/>
@@ -2045,10 +1821,7 @@
       <c r="G48" s="12"/>
       <c r="H48" s="12"/>
       <c r="I48" s="12"/>
-      <c r="J48" s="12"/>
-      <c r="K48" s="12"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="13"/>
+      <c r="J48" s="13"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6"/>
@@ -2060,10 +1833,7 @@
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
-      <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
-      <c r="L49" s="7"/>
-      <c r="M49" s="9"/>
+      <c r="J49" s="9"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10"/>
@@ -2075,10 +1845,7 @@
       <c r="G50" s="12"/>
       <c r="H50" s="12"/>
       <c r="I50" s="12"/>
-      <c r="J50" s="12"/>
-      <c r="K50" s="12"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="13"/>
+      <c r="J50" s="13"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6"/>
@@ -2090,10 +1857,7 @@
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="9"/>
+      <c r="J51" s="9"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10"/>
@@ -2105,10 +1869,7 @@
       <c r="G52" s="12"/>
       <c r="H52" s="12"/>
       <c r="I52" s="12"/>
-      <c r="J52" s="12"/>
-      <c r="K52" s="12"/>
-      <c r="L52" s="11"/>
-      <c r="M52" s="13"/>
+      <c r="J52" s="13"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6"/>
@@ -2120,10 +1881,7 @@
       <c r="G53" s="8"/>
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
-      <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
-      <c r="L53" s="7"/>
-      <c r="M53" s="9"/>
+      <c r="J53" s="9"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10"/>
@@ -2135,10 +1893,7 @@
       <c r="G54" s="12"/>
       <c r="H54" s="12"/>
       <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
-      <c r="K54" s="12"/>
-      <c r="L54" s="11"/>
-      <c r="M54" s="13"/>
+      <c r="J54" s="13"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6"/>
@@ -2150,10 +1905,7 @@
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
-      <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
-      <c r="L55" s="7"/>
-      <c r="M55" s="9"/>
+      <c r="J55" s="9"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10"/>
@@ -2165,10 +1917,7 @@
       <c r="G56" s="12"/>
       <c r="H56" s="12"/>
       <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
-      <c r="K56" s="12"/>
-      <c r="L56" s="11"/>
-      <c r="M56" s="13"/>
+      <c r="J56" s="13"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6"/>
@@ -2180,35 +1929,27 @@
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
-      <c r="J57" s="8"/>
-      <c r="K57" s="8"/>
-      <c r="L57" s="7"/>
-      <c r="M57" s="9"/>
+      <c r="J57" s="9"/>
     </row>
     <row r="60" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="19" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
       <c r="E60" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F60" s="21"/>
       <c r="G60" s="21"/>
-      <c r="H60" s="21"/>
+      <c r="H60" s="22" t="s">
+        <v>42</v>
+      </c>
       <c r="I60" s="21"/>
-      <c r="J60" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="K60" s="21"/>
-      <c r="L60" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="M60" s="21"/>
+      <c r="J60" s="21"/>
     </row>
     <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
@@ -2240,15 +1981,6 @@
       </c>
       <c r="J61" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="K61" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L61" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M61" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2261,10 +1993,7 @@
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
-      <c r="J62" s="8"/>
-      <c r="K62" s="8"/>
-      <c r="L62" s="7"/>
-      <c r="M62" s="9"/>
+      <c r="J62" s="9"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10"/>
@@ -2276,10 +2005,7 @@
       <c r="G63" s="12"/>
       <c r="H63" s="12"/>
       <c r="I63" s="12"/>
-      <c r="J63" s="12"/>
-      <c r="K63" s="12"/>
-      <c r="L63" s="11"/>
-      <c r="M63" s="13"/>
+      <c r="J63" s="13"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6"/>
@@ -2291,10 +2017,7 @@
       <c r="G64" s="8"/>
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
-      <c r="J64" s="8"/>
-      <c r="K64" s="8"/>
-      <c r="L64" s="7"/>
-      <c r="M64" s="9"/>
+      <c r="J64" s="9"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10"/>
@@ -2306,10 +2029,7 @@
       <c r="G65" s="12"/>
       <c r="H65" s="12"/>
       <c r="I65" s="12"/>
-      <c r="J65" s="12"/>
-      <c r="K65" s="12"/>
-      <c r="L65" s="11"/>
-      <c r="M65" s="13"/>
+      <c r="J65" s="13"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6"/>
@@ -2321,10 +2041,7 @@
       <c r="G66" s="8"/>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
-      <c r="J66" s="8"/>
-      <c r="K66" s="8"/>
-      <c r="L66" s="7"/>
-      <c r="M66" s="9"/>
+      <c r="J66" s="9"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10"/>
@@ -2336,10 +2053,7 @@
       <c r="G67" s="12"/>
       <c r="H67" s="12"/>
       <c r="I67" s="12"/>
-      <c r="J67" s="12"/>
-      <c r="K67" s="12"/>
-      <c r="L67" s="11"/>
-      <c r="M67" s="13"/>
+      <c r="J67" s="13"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6"/>
@@ -2351,10 +2065,7 @@
       <c r="G68" s="8"/>
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
-      <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="7"/>
-      <c r="M68" s="9"/>
+      <c r="J68" s="9"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10"/>
@@ -2366,10 +2077,7 @@
       <c r="G69" s="12"/>
       <c r="H69" s="12"/>
       <c r="I69" s="12"/>
-      <c r="J69" s="12"/>
-      <c r="K69" s="12"/>
-      <c r="L69" s="11"/>
-      <c r="M69" s="13"/>
+      <c r="J69" s="13"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6"/>
@@ -2381,10 +2089,7 @@
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
-      <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="7"/>
-      <c r="M70" s="9"/>
+      <c r="J70" s="9"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10"/>
@@ -2396,10 +2101,7 @@
       <c r="G71" s="12"/>
       <c r="H71" s="12"/>
       <c r="I71" s="12"/>
-      <c r="J71" s="12"/>
-      <c r="K71" s="12"/>
-      <c r="L71" s="11"/>
-      <c r="M71" s="13"/>
+      <c r="J71" s="13"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6"/>
@@ -2411,10 +2113,7 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
-      <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="7"/>
-      <c r="M72" s="9"/>
+      <c r="J72" s="9"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10"/>
@@ -2426,10 +2125,7 @@
       <c r="G73" s="12"/>
       <c r="H73" s="12"/>
       <c r="I73" s="12"/>
-      <c r="J73" s="12"/>
-      <c r="K73" s="12"/>
-      <c r="L73" s="11"/>
-      <c r="M73" s="13"/>
+      <c r="J73" s="13"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6"/>
@@ -2441,10 +2137,7 @@
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="7"/>
-      <c r="M74" s="9"/>
+      <c r="J74" s="9"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="10"/>
@@ -2456,10 +2149,7 @@
       <c r="G75" s="12"/>
       <c r="H75" s="12"/>
       <c r="I75" s="12"/>
-      <c r="J75" s="12"/>
-      <c r="K75" s="12"/>
-      <c r="L75" s="11"/>
-      <c r="M75" s="13"/>
+      <c r="J75" s="13"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6"/>
@@ -2471,22 +2161,19 @@
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
       <c r="I76" s="8"/>
-      <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="7"/>
-      <c r="M76" s="9"/>
+      <c r="J76" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="F3:G3"/>
     <mergeCell ref="C22:D22"/>
-    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="F22:G22"/>
     <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="F41:G41"/>
     <mergeCell ref="C60:D60"/>
-    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="F60:G60"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:A19">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -2544,12 +2231,12 @@
       <formula>OR($A62="Accesorios",$A62="Vuelta a la calma")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="20">
+  <dataValidations count="15">
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C3" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K3 M3 K22 M22 K41 M41 K60 M60" type="decimal">
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I3:J3 I22:J22 I41:J41 I60:J60" type="decimal">
       <formula1>0</formula1>
       <formula2>10</formula2>
     </dataValidation>
@@ -2581,14 +2268,6 @@
       <formula1>"Sí"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Minutos del aeróbico (0,5 = 30 s)." errorStyle="stop" errorTitle="Minutos" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J5:J19 J24:J38 J43:J57 J62:J76" type="decimal">
-      <formula1>0</formula1>
-      <formula2>600</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K5:K19" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C22" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -2597,10 +2276,6 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K24:K38" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C41" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -2609,20 +2284,12 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K43:K57" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C60" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Elige un bloque del desplegable." errorStyle="stop" errorTitle="Bloque" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A62:A76" type="list">
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K62:K76" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -2643,27 +2310,25 @@
     <tabColor rgb="FF2F6F9F"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="22" t="n">
+        <v>37</v>
+      </c>
+      <c r="B1" s="23" t="n">
         <f aca="false">'Semana 1'!B1+7</f>
         <v>46335</v>
       </c>
@@ -2672,7 +2337,7 @@
         <v>al 15/11</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
@@ -2680,28 +2345,23 @@
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F3" s="21"/>
       <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
+      <c r="H3" s="22" t="s">
+        <v>42</v>
+      </c>
       <c r="I3" s="21"/>
-      <c r="J3" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="K3" s="21"/>
-      <c r="L3" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="M3" s="21"/>
+      <c r="J3" s="21"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
@@ -2733,15 +2393,6 @@
       </c>
       <c r="J4" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2754,10 +2405,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="9"/>
+      <c r="J5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10"/>
@@ -2769,10 +2417,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="13"/>
+      <c r="J6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6"/>
@@ -2784,10 +2429,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="9"/>
+      <c r="J7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10"/>
@@ -2799,10 +2441,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="13"/>
+      <c r="J8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6"/>
@@ -2814,10 +2453,7 @@
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="9"/>
+      <c r="J9" s="9"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10"/>
@@ -2829,10 +2465,7 @@
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="13"/>
+      <c r="J10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6"/>
@@ -2844,10 +2477,7 @@
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="9"/>
+      <c r="J11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10"/>
@@ -2859,10 +2489,7 @@
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="13"/>
+      <c r="J12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6"/>
@@ -2874,10 +2501,7 @@
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="9"/>
+      <c r="J13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10"/>
@@ -2889,10 +2513,7 @@
       <c r="G14" s="12"/>
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="13"/>
+      <c r="J14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6"/>
@@ -2904,10 +2525,7 @@
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="9"/>
+      <c r="J15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10"/>
@@ -2919,10 +2537,7 @@
       <c r="G16" s="12"/>
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="13"/>
+      <c r="J16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6"/>
@@ -2934,10 +2549,7 @@
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="9"/>
+      <c r="J17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10"/>
@@ -2949,10 +2561,7 @@
       <c r="G18" s="12"/>
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="13"/>
+      <c r="J18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6"/>
@@ -2964,35 +2573,27 @@
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="9"/>
+      <c r="J19" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C22" s="21"/>
       <c r="D22" s="21"/>
       <c r="E22" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F22" s="21"/>
       <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
+      <c r="H22" s="22" t="s">
+        <v>42</v>
+      </c>
       <c r="I22" s="21"/>
-      <c r="J22" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="K22" s="21"/>
-      <c r="L22" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="M22" s="21"/>
+      <c r="J22" s="21"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
@@ -3024,15 +2625,6 @@
       </c>
       <c r="J23" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3045,10 +2637,7 @@
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="9"/>
+      <c r="J24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10"/>
@@ -3060,10 +2649,7 @@
       <c r="G25" s="12"/>
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="13"/>
+      <c r="J25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6"/>
@@ -3075,10 +2661,7 @@
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="9"/>
+      <c r="J26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10"/>
@@ -3090,10 +2673,7 @@
       <c r="G27" s="12"/>
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="13"/>
+      <c r="J27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6"/>
@@ -3105,10 +2685,7 @@
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="9"/>
+      <c r="J28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10"/>
@@ -3120,10 +2697,7 @@
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="13"/>
+      <c r="J29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6"/>
@@ -3135,10 +2709,7 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="9"/>
+      <c r="J30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10"/>
@@ -3150,10 +2721,7 @@
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="13"/>
+      <c r="J31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6"/>
@@ -3165,10 +2733,7 @@
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="9"/>
+      <c r="J32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10"/>
@@ -3180,10 +2745,7 @@
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="13"/>
+      <c r="J33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6"/>
@@ -3195,10 +2757,7 @@
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="9"/>
+      <c r="J34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10"/>
@@ -3210,10 +2769,7 @@
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="13"/>
+      <c r="J35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6"/>
@@ -3225,10 +2781,7 @@
       <c r="G36" s="8"/>
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="9"/>
+      <c r="J36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10"/>
@@ -3240,10 +2793,7 @@
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
       <c r="I37" s="12"/>
-      <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="13"/>
+      <c r="J37" s="13"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6"/>
@@ -3255,35 +2805,27 @@
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="9"/>
+      <c r="J38" s="9"/>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C41" s="21"/>
       <c r="D41" s="21"/>
       <c r="E41" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F41" s="21"/>
       <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
+      <c r="H41" s="22" t="s">
+        <v>42</v>
+      </c>
       <c r="I41" s="21"/>
-      <c r="J41" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="K41" s="21"/>
-      <c r="L41" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="M41" s="21"/>
+      <c r="J41" s="21"/>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
@@ -3315,15 +2857,6 @@
       </c>
       <c r="J42" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="K42" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L42" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3336,10 +2869,7 @@
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="7"/>
-      <c r="M43" s="9"/>
+      <c r="J43" s="9"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10"/>
@@ -3351,10 +2881,7 @@
       <c r="G44" s="12"/>
       <c r="H44" s="12"/>
       <c r="I44" s="12"/>
-      <c r="J44" s="12"/>
-      <c r="K44" s="12"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="13"/>
+      <c r="J44" s="13"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6"/>
@@ -3366,10 +2893,7 @@
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
-      <c r="L45" s="7"/>
-      <c r="M45" s="9"/>
+      <c r="J45" s="9"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10"/>
@@ -3381,10 +2905,7 @@
       <c r="G46" s="12"/>
       <c r="H46" s="12"/>
       <c r="I46" s="12"/>
-      <c r="J46" s="12"/>
-      <c r="K46" s="12"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="13"/>
+      <c r="J46" s="13"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6"/>
@@ -3396,10 +2917,7 @@
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="7"/>
-      <c r="M47" s="9"/>
+      <c r="J47" s="9"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10"/>
@@ -3411,10 +2929,7 @@
       <c r="G48" s="12"/>
       <c r="H48" s="12"/>
       <c r="I48" s="12"/>
-      <c r="J48" s="12"/>
-      <c r="K48" s="12"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="13"/>
+      <c r="J48" s="13"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6"/>
@@ -3426,10 +2941,7 @@
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
-      <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
-      <c r="L49" s="7"/>
-      <c r="M49" s="9"/>
+      <c r="J49" s="9"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10"/>
@@ -3441,10 +2953,7 @@
       <c r="G50" s="12"/>
       <c r="H50" s="12"/>
       <c r="I50" s="12"/>
-      <c r="J50" s="12"/>
-      <c r="K50" s="12"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="13"/>
+      <c r="J50" s="13"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6"/>
@@ -3456,10 +2965,7 @@
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="9"/>
+      <c r="J51" s="9"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10"/>
@@ -3471,10 +2977,7 @@
       <c r="G52" s="12"/>
       <c r="H52" s="12"/>
       <c r="I52" s="12"/>
-      <c r="J52" s="12"/>
-      <c r="K52" s="12"/>
-      <c r="L52" s="11"/>
-      <c r="M52" s="13"/>
+      <c r="J52" s="13"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6"/>
@@ -3486,10 +2989,7 @@
       <c r="G53" s="8"/>
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
-      <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
-      <c r="L53" s="7"/>
-      <c r="M53" s="9"/>
+      <c r="J53" s="9"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10"/>
@@ -3501,10 +3001,7 @@
       <c r="G54" s="12"/>
       <c r="H54" s="12"/>
       <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
-      <c r="K54" s="12"/>
-      <c r="L54" s="11"/>
-      <c r="M54" s="13"/>
+      <c r="J54" s="13"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6"/>
@@ -3516,10 +3013,7 @@
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
-      <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
-      <c r="L55" s="7"/>
-      <c r="M55" s="9"/>
+      <c r="J55" s="9"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10"/>
@@ -3531,10 +3025,7 @@
       <c r="G56" s="12"/>
       <c r="H56" s="12"/>
       <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
-      <c r="K56" s="12"/>
-      <c r="L56" s="11"/>
-      <c r="M56" s="13"/>
+      <c r="J56" s="13"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6"/>
@@ -3546,35 +3037,27 @@
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
-      <c r="J57" s="8"/>
-      <c r="K57" s="8"/>
-      <c r="L57" s="7"/>
-      <c r="M57" s="9"/>
+      <c r="J57" s="9"/>
     </row>
     <row r="60" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="19" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
       <c r="E60" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F60" s="21"/>
       <c r="G60" s="21"/>
-      <c r="H60" s="21"/>
+      <c r="H60" s="22" t="s">
+        <v>42</v>
+      </c>
       <c r="I60" s="21"/>
-      <c r="J60" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="K60" s="21"/>
-      <c r="L60" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="M60" s="21"/>
+      <c r="J60" s="21"/>
     </row>
     <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
@@ -3606,15 +3089,6 @@
       </c>
       <c r="J61" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="K61" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L61" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M61" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3627,10 +3101,7 @@
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
-      <c r="J62" s="8"/>
-      <c r="K62" s="8"/>
-      <c r="L62" s="7"/>
-      <c r="M62" s="9"/>
+      <c r="J62" s="9"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10"/>
@@ -3642,10 +3113,7 @@
       <c r="G63" s="12"/>
       <c r="H63" s="12"/>
       <c r="I63" s="12"/>
-      <c r="J63" s="12"/>
-      <c r="K63" s="12"/>
-      <c r="L63" s="11"/>
-      <c r="M63" s="13"/>
+      <c r="J63" s="13"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6"/>
@@ -3657,10 +3125,7 @@
       <c r="G64" s="8"/>
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
-      <c r="J64" s="8"/>
-      <c r="K64" s="8"/>
-      <c r="L64" s="7"/>
-      <c r="M64" s="9"/>
+      <c r="J64" s="9"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10"/>
@@ -3672,10 +3137,7 @@
       <c r="G65" s="12"/>
       <c r="H65" s="12"/>
       <c r="I65" s="12"/>
-      <c r="J65" s="12"/>
-      <c r="K65" s="12"/>
-      <c r="L65" s="11"/>
-      <c r="M65" s="13"/>
+      <c r="J65" s="13"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6"/>
@@ -3687,10 +3149,7 @@
       <c r="G66" s="8"/>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
-      <c r="J66" s="8"/>
-      <c r="K66" s="8"/>
-      <c r="L66" s="7"/>
-      <c r="M66" s="9"/>
+      <c r="J66" s="9"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10"/>
@@ -3702,10 +3161,7 @@
       <c r="G67" s="12"/>
       <c r="H67" s="12"/>
       <c r="I67" s="12"/>
-      <c r="J67" s="12"/>
-      <c r="K67" s="12"/>
-      <c r="L67" s="11"/>
-      <c r="M67" s="13"/>
+      <c r="J67" s="13"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6"/>
@@ -3717,10 +3173,7 @@
       <c r="G68" s="8"/>
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
-      <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="7"/>
-      <c r="M68" s="9"/>
+      <c r="J68" s="9"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10"/>
@@ -3732,10 +3185,7 @@
       <c r="G69" s="12"/>
       <c r="H69" s="12"/>
       <c r="I69" s="12"/>
-      <c r="J69" s="12"/>
-      <c r="K69" s="12"/>
-      <c r="L69" s="11"/>
-      <c r="M69" s="13"/>
+      <c r="J69" s="13"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6"/>
@@ -3747,10 +3197,7 @@
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
-      <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="7"/>
-      <c r="M70" s="9"/>
+      <c r="J70" s="9"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10"/>
@@ -3762,10 +3209,7 @@
       <c r="G71" s="12"/>
       <c r="H71" s="12"/>
       <c r="I71" s="12"/>
-      <c r="J71" s="12"/>
-      <c r="K71" s="12"/>
-      <c r="L71" s="11"/>
-      <c r="M71" s="13"/>
+      <c r="J71" s="13"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6"/>
@@ -3777,10 +3221,7 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
-      <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="7"/>
-      <c r="M72" s="9"/>
+      <c r="J72" s="9"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10"/>
@@ -3792,10 +3233,7 @@
       <c r="G73" s="12"/>
       <c r="H73" s="12"/>
       <c r="I73" s="12"/>
-      <c r="J73" s="12"/>
-      <c r="K73" s="12"/>
-      <c r="L73" s="11"/>
-      <c r="M73" s="13"/>
+      <c r="J73" s="13"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6"/>
@@ -3807,10 +3245,7 @@
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="7"/>
-      <c r="M74" s="9"/>
+      <c r="J74" s="9"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="10"/>
@@ -3822,10 +3257,7 @@
       <c r="G75" s="12"/>
       <c r="H75" s="12"/>
       <c r="I75" s="12"/>
-      <c r="J75" s="12"/>
-      <c r="K75" s="12"/>
-      <c r="L75" s="11"/>
-      <c r="M75" s="13"/>
+      <c r="J75" s="13"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6"/>
@@ -3837,22 +3269,19 @@
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
       <c r="I76" s="8"/>
-      <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="7"/>
-      <c r="M76" s="9"/>
+      <c r="J76" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="F3:G3"/>
     <mergeCell ref="C22:D22"/>
-    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="F22:G22"/>
     <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="F41:G41"/>
     <mergeCell ref="C60:D60"/>
-    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="F60:G60"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:A19">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -3910,8 +3339,8 @@
       <formula>OR($A62="Accesorios",$A62="Vuelta a la calma")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="20">
-    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K3 M3 K22 M22 K41 M41 K60 M60" type="decimal">
+  <dataValidations count="15">
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I3:J3 I22:J22 I41:J41 I60:J60" type="decimal">
       <formula1>0</formula1>
       <formula2>10</formula2>
     </dataValidation>
@@ -3939,10 +3368,6 @@
       <formula1>"Sí"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Minutos del aeróbico (0,5 = 30 s)." errorStyle="stop" errorTitle="Minutos" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J5:J19 J24:J38 J43:J57 J62:J76" type="decimal">
-      <formula1>0</formula1>
-      <formula2>600</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C3" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -3951,10 +3376,6 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K5:K19" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C22" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -3963,10 +3384,6 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K24:K38" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C41" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -3975,20 +3392,12 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K43:K57" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C60" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Elige un bloque del desplegable." errorStyle="stop" errorTitle="Bloque" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A62:A76" type="list">
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K62:K76" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -4008,27 +3417,25 @@
     <tabColor rgb="FF2E8B6E"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="22" t="n">
+        <v>37</v>
+      </c>
+      <c r="B1" s="23" t="n">
         <f aca="false">'Semana 2'!B1+7</f>
         <v>46342</v>
       </c>
@@ -4037,7 +3444,7 @@
         <v>al 22/11</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
@@ -4045,28 +3452,23 @@
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F3" s="21"/>
       <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
+      <c r="H3" s="22" t="s">
+        <v>42</v>
+      </c>
       <c r="I3" s="21"/>
-      <c r="J3" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="K3" s="21"/>
-      <c r="L3" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="M3" s="21"/>
+      <c r="J3" s="21"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
@@ -4098,15 +3500,6 @@
       </c>
       <c r="J4" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4119,10 +3512,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="9"/>
+      <c r="J5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10"/>
@@ -4134,10 +3524,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="13"/>
+      <c r="J6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6"/>
@@ -4149,10 +3536,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="9"/>
+      <c r="J7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10"/>
@@ -4164,10 +3548,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="13"/>
+      <c r="J8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6"/>
@@ -4179,10 +3560,7 @@
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="9"/>
+      <c r="J9" s="9"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10"/>
@@ -4194,10 +3572,7 @@
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="13"/>
+      <c r="J10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6"/>
@@ -4209,10 +3584,7 @@
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="9"/>
+      <c r="J11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10"/>
@@ -4224,10 +3596,7 @@
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="13"/>
+      <c r="J12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6"/>
@@ -4239,10 +3608,7 @@
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="9"/>
+      <c r="J13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10"/>
@@ -4254,10 +3620,7 @@
       <c r="G14" s="12"/>
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="13"/>
+      <c r="J14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6"/>
@@ -4269,10 +3632,7 @@
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="9"/>
+      <c r="J15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10"/>
@@ -4284,10 +3644,7 @@
       <c r="G16" s="12"/>
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="13"/>
+      <c r="J16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6"/>
@@ -4299,10 +3656,7 @@
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="9"/>
+      <c r="J17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10"/>
@@ -4314,10 +3668,7 @@
       <c r="G18" s="12"/>
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="13"/>
+      <c r="J18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6"/>
@@ -4329,35 +3680,27 @@
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="9"/>
+      <c r="J19" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C22" s="21"/>
       <c r="D22" s="21"/>
       <c r="E22" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F22" s="21"/>
       <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
+      <c r="H22" s="22" t="s">
+        <v>42</v>
+      </c>
       <c r="I22" s="21"/>
-      <c r="J22" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="K22" s="21"/>
-      <c r="L22" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="M22" s="21"/>
+      <c r="J22" s="21"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
@@ -4389,15 +3732,6 @@
       </c>
       <c r="J23" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4410,10 +3744,7 @@
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="9"/>
+      <c r="J24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10"/>
@@ -4425,10 +3756,7 @@
       <c r="G25" s="12"/>
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="13"/>
+      <c r="J25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6"/>
@@ -4440,10 +3768,7 @@
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="9"/>
+      <c r="J26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10"/>
@@ -4455,10 +3780,7 @@
       <c r="G27" s="12"/>
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="13"/>
+      <c r="J27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6"/>
@@ -4470,10 +3792,7 @@
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="9"/>
+      <c r="J28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10"/>
@@ -4485,10 +3804,7 @@
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="13"/>
+      <c r="J29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6"/>
@@ -4500,10 +3816,7 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="9"/>
+      <c r="J30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10"/>
@@ -4515,10 +3828,7 @@
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="13"/>
+      <c r="J31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6"/>
@@ -4530,10 +3840,7 @@
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="9"/>
+      <c r="J32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10"/>
@@ -4545,10 +3852,7 @@
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="13"/>
+      <c r="J33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6"/>
@@ -4560,10 +3864,7 @@
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="9"/>
+      <c r="J34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10"/>
@@ -4575,10 +3876,7 @@
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="13"/>
+      <c r="J35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6"/>
@@ -4590,10 +3888,7 @@
       <c r="G36" s="8"/>
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="9"/>
+      <c r="J36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10"/>
@@ -4605,10 +3900,7 @@
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
       <c r="I37" s="12"/>
-      <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="13"/>
+      <c r="J37" s="13"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6"/>
@@ -4620,35 +3912,27 @@
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="9"/>
+      <c r="J38" s="9"/>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C41" s="21"/>
       <c r="D41" s="21"/>
       <c r="E41" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F41" s="21"/>
       <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
+      <c r="H41" s="22" t="s">
+        <v>42</v>
+      </c>
       <c r="I41" s="21"/>
-      <c r="J41" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="K41" s="21"/>
-      <c r="L41" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="M41" s="21"/>
+      <c r="J41" s="21"/>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
@@ -4680,15 +3964,6 @@
       </c>
       <c r="J42" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="K42" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L42" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4701,10 +3976,7 @@
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="7"/>
-      <c r="M43" s="9"/>
+      <c r="J43" s="9"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10"/>
@@ -4716,10 +3988,7 @@
       <c r="G44" s="12"/>
       <c r="H44" s="12"/>
       <c r="I44" s="12"/>
-      <c r="J44" s="12"/>
-      <c r="K44" s="12"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="13"/>
+      <c r="J44" s="13"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6"/>
@@ -4731,10 +4000,7 @@
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
-      <c r="L45" s="7"/>
-      <c r="M45" s="9"/>
+      <c r="J45" s="9"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10"/>
@@ -4746,10 +4012,7 @@
       <c r="G46" s="12"/>
       <c r="H46" s="12"/>
       <c r="I46" s="12"/>
-      <c r="J46" s="12"/>
-      <c r="K46" s="12"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="13"/>
+      <c r="J46" s="13"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6"/>
@@ -4761,10 +4024,7 @@
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="7"/>
-      <c r="M47" s="9"/>
+      <c r="J47" s="9"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10"/>
@@ -4776,10 +4036,7 @@
       <c r="G48" s="12"/>
       <c r="H48" s="12"/>
       <c r="I48" s="12"/>
-      <c r="J48" s="12"/>
-      <c r="K48" s="12"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="13"/>
+      <c r="J48" s="13"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6"/>
@@ -4791,10 +4048,7 @@
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
-      <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
-      <c r="L49" s="7"/>
-      <c r="M49" s="9"/>
+      <c r="J49" s="9"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10"/>
@@ -4806,10 +4060,7 @@
       <c r="G50" s="12"/>
       <c r="H50" s="12"/>
       <c r="I50" s="12"/>
-      <c r="J50" s="12"/>
-      <c r="K50" s="12"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="13"/>
+      <c r="J50" s="13"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6"/>
@@ -4821,10 +4072,7 @@
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="9"/>
+      <c r="J51" s="9"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10"/>
@@ -4836,10 +4084,7 @@
       <c r="G52" s="12"/>
       <c r="H52" s="12"/>
       <c r="I52" s="12"/>
-      <c r="J52" s="12"/>
-      <c r="K52" s="12"/>
-      <c r="L52" s="11"/>
-      <c r="M52" s="13"/>
+      <c r="J52" s="13"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6"/>
@@ -4851,10 +4096,7 @@
       <c r="G53" s="8"/>
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
-      <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
-      <c r="L53" s="7"/>
-      <c r="M53" s="9"/>
+      <c r="J53" s="9"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10"/>
@@ -4866,10 +4108,7 @@
       <c r="G54" s="12"/>
       <c r="H54" s="12"/>
       <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
-      <c r="K54" s="12"/>
-      <c r="L54" s="11"/>
-      <c r="M54" s="13"/>
+      <c r="J54" s="13"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6"/>
@@ -4881,10 +4120,7 @@
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
-      <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
-      <c r="L55" s="7"/>
-      <c r="M55" s="9"/>
+      <c r="J55" s="9"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10"/>
@@ -4896,10 +4132,7 @@
       <c r="G56" s="12"/>
       <c r="H56" s="12"/>
       <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
-      <c r="K56" s="12"/>
-      <c r="L56" s="11"/>
-      <c r="M56" s="13"/>
+      <c r="J56" s="13"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6"/>
@@ -4911,35 +4144,27 @@
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
-      <c r="J57" s="8"/>
-      <c r="K57" s="8"/>
-      <c r="L57" s="7"/>
-      <c r="M57" s="9"/>
+      <c r="J57" s="9"/>
     </row>
     <row r="60" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="19" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
       <c r="E60" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F60" s="21"/>
       <c r="G60" s="21"/>
-      <c r="H60" s="21"/>
+      <c r="H60" s="22" t="s">
+        <v>42</v>
+      </c>
       <c r="I60" s="21"/>
-      <c r="J60" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="K60" s="21"/>
-      <c r="L60" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="M60" s="21"/>
+      <c r="J60" s="21"/>
     </row>
     <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
@@ -4971,15 +4196,6 @@
       </c>
       <c r="J61" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="K61" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L61" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M61" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4992,10 +4208,7 @@
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
-      <c r="J62" s="8"/>
-      <c r="K62" s="8"/>
-      <c r="L62" s="7"/>
-      <c r="M62" s="9"/>
+      <c r="J62" s="9"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10"/>
@@ -5007,10 +4220,7 @@
       <c r="G63" s="12"/>
       <c r="H63" s="12"/>
       <c r="I63" s="12"/>
-      <c r="J63" s="12"/>
-      <c r="K63" s="12"/>
-      <c r="L63" s="11"/>
-      <c r="M63" s="13"/>
+      <c r="J63" s="13"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6"/>
@@ -5022,10 +4232,7 @@
       <c r="G64" s="8"/>
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
-      <c r="J64" s="8"/>
-      <c r="K64" s="8"/>
-      <c r="L64" s="7"/>
-      <c r="M64" s="9"/>
+      <c r="J64" s="9"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10"/>
@@ -5037,10 +4244,7 @@
       <c r="G65" s="12"/>
       <c r="H65" s="12"/>
       <c r="I65" s="12"/>
-      <c r="J65" s="12"/>
-      <c r="K65" s="12"/>
-      <c r="L65" s="11"/>
-      <c r="M65" s="13"/>
+      <c r="J65" s="13"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6"/>
@@ -5052,10 +4256,7 @@
       <c r="G66" s="8"/>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
-      <c r="J66" s="8"/>
-      <c r="K66" s="8"/>
-      <c r="L66" s="7"/>
-      <c r="M66" s="9"/>
+      <c r="J66" s="9"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10"/>
@@ -5067,10 +4268,7 @@
       <c r="G67" s="12"/>
       <c r="H67" s="12"/>
       <c r="I67" s="12"/>
-      <c r="J67" s="12"/>
-      <c r="K67" s="12"/>
-      <c r="L67" s="11"/>
-      <c r="M67" s="13"/>
+      <c r="J67" s="13"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6"/>
@@ -5082,10 +4280,7 @@
       <c r="G68" s="8"/>
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
-      <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="7"/>
-      <c r="M68" s="9"/>
+      <c r="J68" s="9"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10"/>
@@ -5097,10 +4292,7 @@
       <c r="G69" s="12"/>
       <c r="H69" s="12"/>
       <c r="I69" s="12"/>
-      <c r="J69" s="12"/>
-      <c r="K69" s="12"/>
-      <c r="L69" s="11"/>
-      <c r="M69" s="13"/>
+      <c r="J69" s="13"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6"/>
@@ -5112,10 +4304,7 @@
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
-      <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="7"/>
-      <c r="M70" s="9"/>
+      <c r="J70" s="9"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10"/>
@@ -5127,10 +4316,7 @@
       <c r="G71" s="12"/>
       <c r="H71" s="12"/>
       <c r="I71" s="12"/>
-      <c r="J71" s="12"/>
-      <c r="K71" s="12"/>
-      <c r="L71" s="11"/>
-      <c r="M71" s="13"/>
+      <c r="J71" s="13"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6"/>
@@ -5142,10 +4328,7 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
-      <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="7"/>
-      <c r="M72" s="9"/>
+      <c r="J72" s="9"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10"/>
@@ -5157,10 +4340,7 @@
       <c r="G73" s="12"/>
       <c r="H73" s="12"/>
       <c r="I73" s="12"/>
-      <c r="J73" s="12"/>
-      <c r="K73" s="12"/>
-      <c r="L73" s="11"/>
-      <c r="M73" s="13"/>
+      <c r="J73" s="13"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6"/>
@@ -5172,10 +4352,7 @@
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="7"/>
-      <c r="M74" s="9"/>
+      <c r="J74" s="9"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="10"/>
@@ -5187,10 +4364,7 @@
       <c r="G75" s="12"/>
       <c r="H75" s="12"/>
       <c r="I75" s="12"/>
-      <c r="J75" s="12"/>
-      <c r="K75" s="12"/>
-      <c r="L75" s="11"/>
-      <c r="M75" s="13"/>
+      <c r="J75" s="13"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6"/>
@@ -5202,22 +4376,19 @@
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
       <c r="I76" s="8"/>
-      <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="7"/>
-      <c r="M76" s="9"/>
+      <c r="J76" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="F3:G3"/>
     <mergeCell ref="C22:D22"/>
-    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="F22:G22"/>
     <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="F41:G41"/>
     <mergeCell ref="C60:D60"/>
-    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="F60:G60"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:A19">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -5275,8 +4446,8 @@
       <formula>OR($A62="Accesorios",$A62="Vuelta a la calma")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="20">
-    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K3 M3 K22 M22 K41 M41 K60 M60" type="decimal">
+  <dataValidations count="15">
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I3:J3 I22:J22 I41:J41 I60:J60" type="decimal">
       <formula1>0</formula1>
       <formula2>10</formula2>
     </dataValidation>
@@ -5304,10 +4475,6 @@
       <formula1>"Sí"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Minutos del aeróbico (0,5 = 30 s)." errorStyle="stop" errorTitle="Minutos" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J5:J19 J24:J38 J43:J57 J62:J76" type="decimal">
-      <formula1>0</formula1>
-      <formula2>600</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C3" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -5316,10 +4483,6 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K5:K19" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C22" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -5328,10 +4491,6 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K24:K38" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C41" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -5340,20 +4499,12 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K43:K57" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C60" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Elige un bloque del desplegable." errorStyle="stop" errorTitle="Bloque" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A62:A76" type="list">
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K62:K76" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -5373,27 +4524,25 @@
     <tabColor rgb="FF2F6F9F"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="22" t="n">
+        <v>37</v>
+      </c>
+      <c r="B1" s="23" t="n">
         <f aca="false">'Semana 3'!B1+7</f>
         <v>46349</v>
       </c>
@@ -5402,7 +4551,7 @@
         <v>al 29/11</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
@@ -5410,28 +4559,23 @@
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F3" s="21"/>
       <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
+      <c r="H3" s="22" t="s">
+        <v>42</v>
+      </c>
       <c r="I3" s="21"/>
-      <c r="J3" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="K3" s="21"/>
-      <c r="L3" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="M3" s="21"/>
+      <c r="J3" s="21"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
@@ -5463,15 +4607,6 @@
       </c>
       <c r="J4" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5484,10 +4619,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="9"/>
+      <c r="J5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10"/>
@@ -5499,10 +4631,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="13"/>
+      <c r="J6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6"/>
@@ -5514,10 +4643,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="9"/>
+      <c r="J7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10"/>
@@ -5529,10 +4655,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="13"/>
+      <c r="J8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6"/>
@@ -5544,10 +4667,7 @@
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="9"/>
+      <c r="J9" s="9"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10"/>
@@ -5559,10 +4679,7 @@
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="13"/>
+      <c r="J10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6"/>
@@ -5574,10 +4691,7 @@
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="9"/>
+      <c r="J11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10"/>
@@ -5589,10 +4703,7 @@
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="13"/>
+      <c r="J12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6"/>
@@ -5604,10 +4715,7 @@
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="9"/>
+      <c r="J13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10"/>
@@ -5619,10 +4727,7 @@
       <c r="G14" s="12"/>
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="13"/>
+      <c r="J14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6"/>
@@ -5634,10 +4739,7 @@
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="9"/>
+      <c r="J15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10"/>
@@ -5649,10 +4751,7 @@
       <c r="G16" s="12"/>
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="13"/>
+      <c r="J16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6"/>
@@ -5664,10 +4763,7 @@
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="9"/>
+      <c r="J17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10"/>
@@ -5679,10 +4775,7 @@
       <c r="G18" s="12"/>
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="13"/>
+      <c r="J18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6"/>
@@ -5694,35 +4787,27 @@
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="9"/>
+      <c r="J19" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C22" s="21"/>
       <c r="D22" s="21"/>
       <c r="E22" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F22" s="21"/>
       <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
+      <c r="H22" s="22" t="s">
+        <v>42</v>
+      </c>
       <c r="I22" s="21"/>
-      <c r="J22" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="K22" s="21"/>
-      <c r="L22" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="M22" s="21"/>
+      <c r="J22" s="21"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
@@ -5754,15 +4839,6 @@
       </c>
       <c r="J23" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5775,10 +4851,7 @@
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="9"/>
+      <c r="J24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10"/>
@@ -5790,10 +4863,7 @@
       <c r="G25" s="12"/>
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="13"/>
+      <c r="J25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6"/>
@@ -5805,10 +4875,7 @@
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="9"/>
+      <c r="J26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10"/>
@@ -5820,10 +4887,7 @@
       <c r="G27" s="12"/>
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="13"/>
+      <c r="J27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6"/>
@@ -5835,10 +4899,7 @@
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="9"/>
+      <c r="J28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10"/>
@@ -5850,10 +4911,7 @@
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="13"/>
+      <c r="J29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6"/>
@@ -5865,10 +4923,7 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="9"/>
+      <c r="J30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10"/>
@@ -5880,10 +4935,7 @@
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="13"/>
+      <c r="J31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6"/>
@@ -5895,10 +4947,7 @@
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="9"/>
+      <c r="J32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10"/>
@@ -5910,10 +4959,7 @@
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="13"/>
+      <c r="J33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6"/>
@@ -5925,10 +4971,7 @@
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="9"/>
+      <c r="J34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10"/>
@@ -5940,10 +4983,7 @@
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="13"/>
+      <c r="J35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6"/>
@@ -5955,10 +4995,7 @@
       <c r="G36" s="8"/>
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="9"/>
+      <c r="J36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10"/>
@@ -5970,10 +5007,7 @@
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
       <c r="I37" s="12"/>
-      <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="13"/>
+      <c r="J37" s="13"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6"/>
@@ -5985,35 +5019,27 @@
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="9"/>
+      <c r="J38" s="9"/>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C41" s="21"/>
       <c r="D41" s="21"/>
       <c r="E41" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F41" s="21"/>
       <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
+      <c r="H41" s="22" t="s">
+        <v>42</v>
+      </c>
       <c r="I41" s="21"/>
-      <c r="J41" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="K41" s="21"/>
-      <c r="L41" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="M41" s="21"/>
+      <c r="J41" s="21"/>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
@@ -6045,15 +5071,6 @@
       </c>
       <c r="J42" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="K42" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L42" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6066,10 +5083,7 @@
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="7"/>
-      <c r="M43" s="9"/>
+      <c r="J43" s="9"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10"/>
@@ -6081,10 +5095,7 @@
       <c r="G44" s="12"/>
       <c r="H44" s="12"/>
       <c r="I44" s="12"/>
-      <c r="J44" s="12"/>
-      <c r="K44" s="12"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="13"/>
+      <c r="J44" s="13"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6"/>
@@ -6096,10 +5107,7 @@
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
-      <c r="L45" s="7"/>
-      <c r="M45" s="9"/>
+      <c r="J45" s="9"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10"/>
@@ -6111,10 +5119,7 @@
       <c r="G46" s="12"/>
       <c r="H46" s="12"/>
       <c r="I46" s="12"/>
-      <c r="J46" s="12"/>
-      <c r="K46" s="12"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="13"/>
+      <c r="J46" s="13"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6"/>
@@ -6126,10 +5131,7 @@
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="7"/>
-      <c r="M47" s="9"/>
+      <c r="J47" s="9"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10"/>
@@ -6141,10 +5143,7 @@
       <c r="G48" s="12"/>
       <c r="H48" s="12"/>
       <c r="I48" s="12"/>
-      <c r="J48" s="12"/>
-      <c r="K48" s="12"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="13"/>
+      <c r="J48" s="13"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6"/>
@@ -6156,10 +5155,7 @@
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
-      <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
-      <c r="L49" s="7"/>
-      <c r="M49" s="9"/>
+      <c r="J49" s="9"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10"/>
@@ -6171,10 +5167,7 @@
       <c r="G50" s="12"/>
       <c r="H50" s="12"/>
       <c r="I50" s="12"/>
-      <c r="J50" s="12"/>
-      <c r="K50" s="12"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="13"/>
+      <c r="J50" s="13"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6"/>
@@ -6186,10 +5179,7 @@
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="9"/>
+      <c r="J51" s="9"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10"/>
@@ -6201,10 +5191,7 @@
       <c r="G52" s="12"/>
       <c r="H52" s="12"/>
       <c r="I52" s="12"/>
-      <c r="J52" s="12"/>
-      <c r="K52" s="12"/>
-      <c r="L52" s="11"/>
-      <c r="M52" s="13"/>
+      <c r="J52" s="13"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6"/>
@@ -6216,10 +5203,7 @@
       <c r="G53" s="8"/>
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
-      <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
-      <c r="L53" s="7"/>
-      <c r="M53" s="9"/>
+      <c r="J53" s="9"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10"/>
@@ -6231,10 +5215,7 @@
       <c r="G54" s="12"/>
       <c r="H54" s="12"/>
       <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
-      <c r="K54" s="12"/>
-      <c r="L54" s="11"/>
-      <c r="M54" s="13"/>
+      <c r="J54" s="13"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6"/>
@@ -6246,10 +5227,7 @@
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
-      <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
-      <c r="L55" s="7"/>
-      <c r="M55" s="9"/>
+      <c r="J55" s="9"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10"/>
@@ -6261,10 +5239,7 @@
       <c r="G56" s="12"/>
       <c r="H56" s="12"/>
       <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
-      <c r="K56" s="12"/>
-      <c r="L56" s="11"/>
-      <c r="M56" s="13"/>
+      <c r="J56" s="13"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6"/>
@@ -6276,35 +5251,27 @@
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
-      <c r="J57" s="8"/>
-      <c r="K57" s="8"/>
-      <c r="L57" s="7"/>
-      <c r="M57" s="9"/>
+      <c r="J57" s="9"/>
     </row>
     <row r="60" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="19" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
       <c r="E60" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F60" s="21"/>
       <c r="G60" s="21"/>
-      <c r="H60" s="21"/>
+      <c r="H60" s="22" t="s">
+        <v>42</v>
+      </c>
       <c r="I60" s="21"/>
-      <c r="J60" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="K60" s="21"/>
-      <c r="L60" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="M60" s="21"/>
+      <c r="J60" s="21"/>
     </row>
     <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
@@ -6336,15 +5303,6 @@
       </c>
       <c r="J61" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="K61" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L61" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M61" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6357,10 +5315,7 @@
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
-      <c r="J62" s="8"/>
-      <c r="K62" s="8"/>
-      <c r="L62" s="7"/>
-      <c r="M62" s="9"/>
+      <c r="J62" s="9"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10"/>
@@ -6372,10 +5327,7 @@
       <c r="G63" s="12"/>
       <c r="H63" s="12"/>
       <c r="I63" s="12"/>
-      <c r="J63" s="12"/>
-      <c r="K63" s="12"/>
-      <c r="L63" s="11"/>
-      <c r="M63" s="13"/>
+      <c r="J63" s="13"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6"/>
@@ -6387,10 +5339,7 @@
       <c r="G64" s="8"/>
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
-      <c r="J64" s="8"/>
-      <c r="K64" s="8"/>
-      <c r="L64" s="7"/>
-      <c r="M64" s="9"/>
+      <c r="J64" s="9"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10"/>
@@ -6402,10 +5351,7 @@
       <c r="G65" s="12"/>
       <c r="H65" s="12"/>
       <c r="I65" s="12"/>
-      <c r="J65" s="12"/>
-      <c r="K65" s="12"/>
-      <c r="L65" s="11"/>
-      <c r="M65" s="13"/>
+      <c r="J65" s="13"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6"/>
@@ -6417,10 +5363,7 @@
       <c r="G66" s="8"/>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
-      <c r="J66" s="8"/>
-      <c r="K66" s="8"/>
-      <c r="L66" s="7"/>
-      <c r="M66" s="9"/>
+      <c r="J66" s="9"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10"/>
@@ -6432,10 +5375,7 @@
       <c r="G67" s="12"/>
       <c r="H67" s="12"/>
       <c r="I67" s="12"/>
-      <c r="J67" s="12"/>
-      <c r="K67" s="12"/>
-      <c r="L67" s="11"/>
-      <c r="M67" s="13"/>
+      <c r="J67" s="13"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6"/>
@@ -6447,10 +5387,7 @@
       <c r="G68" s="8"/>
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
-      <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="7"/>
-      <c r="M68" s="9"/>
+      <c r="J68" s="9"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10"/>
@@ -6462,10 +5399,7 @@
       <c r="G69" s="12"/>
       <c r="H69" s="12"/>
       <c r="I69" s="12"/>
-      <c r="J69" s="12"/>
-      <c r="K69" s="12"/>
-      <c r="L69" s="11"/>
-      <c r="M69" s="13"/>
+      <c r="J69" s="13"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6"/>
@@ -6477,10 +5411,7 @@
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
-      <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="7"/>
-      <c r="M70" s="9"/>
+      <c r="J70" s="9"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10"/>
@@ -6492,10 +5423,7 @@
       <c r="G71" s="12"/>
       <c r="H71" s="12"/>
       <c r="I71" s="12"/>
-      <c r="J71" s="12"/>
-      <c r="K71" s="12"/>
-      <c r="L71" s="11"/>
-      <c r="M71" s="13"/>
+      <c r="J71" s="13"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6"/>
@@ -6507,10 +5435,7 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
-      <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="7"/>
-      <c r="M72" s="9"/>
+      <c r="J72" s="9"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10"/>
@@ -6522,10 +5447,7 @@
       <c r="G73" s="12"/>
       <c r="H73" s="12"/>
       <c r="I73" s="12"/>
-      <c r="J73" s="12"/>
-      <c r="K73" s="12"/>
-      <c r="L73" s="11"/>
-      <c r="M73" s="13"/>
+      <c r="J73" s="13"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6"/>
@@ -6537,10 +5459,7 @@
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="7"/>
-      <c r="M74" s="9"/>
+      <c r="J74" s="9"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="10"/>
@@ -6552,10 +5471,7 @@
       <c r="G75" s="12"/>
       <c r="H75" s="12"/>
       <c r="I75" s="12"/>
-      <c r="J75" s="12"/>
-      <c r="K75" s="12"/>
-      <c r="L75" s="11"/>
-      <c r="M75" s="13"/>
+      <c r="J75" s="13"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6"/>
@@ -6567,22 +5483,19 @@
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
       <c r="I76" s="8"/>
-      <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="7"/>
-      <c r="M76" s="9"/>
+      <c r="J76" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="F3:G3"/>
     <mergeCell ref="C22:D22"/>
-    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="F22:G22"/>
     <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="F41:G41"/>
     <mergeCell ref="C60:D60"/>
-    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="F60:G60"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:A19">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -6640,8 +5553,8 @@
       <formula>OR($A62="Accesorios",$A62="Vuelta a la calma")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="20">
-    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K3 M3 K22 M22 K41 M41 K60 M60" type="decimal">
+  <dataValidations count="15">
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I3:J3 I22:J22 I41:J41 I60:J60" type="decimal">
       <formula1>0</formula1>
       <formula2>10</formula2>
     </dataValidation>
@@ -6669,10 +5582,6 @@
       <formula1>"Sí"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Minutos del aeróbico (0,5 = 30 s)." errorStyle="stop" errorTitle="Minutos" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J5:J19 J24:J38 J43:J57 J62:J76" type="decimal">
-      <formula1>0</formula1>
-      <formula2>600</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C3" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -6681,10 +5590,6 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K5:K19" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C22" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -6693,10 +5598,6 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K24:K38" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C41" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -6705,20 +5606,12 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K43:K57" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C60" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Elige un bloque del desplegable." errorStyle="stop" errorTitle="Bloque" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A62:A76" type="list">
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K62:K76" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -6738,27 +5631,25 @@
     <tabColor rgb="FF2E8B6E"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="22" t="n">
+        <v>37</v>
+      </c>
+      <c r="B1" s="23" t="n">
         <f aca="false">'Semana 4'!B1+7</f>
         <v>46356</v>
       </c>
@@ -6767,7 +5658,7 @@
         <v>al 06/12</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
@@ -6775,28 +5666,23 @@
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F3" s="21"/>
       <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
+      <c r="H3" s="22" t="s">
+        <v>42</v>
+      </c>
       <c r="I3" s="21"/>
-      <c r="J3" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="K3" s="21"/>
-      <c r="L3" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="M3" s="21"/>
+      <c r="J3" s="21"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
@@ -6828,15 +5714,6 @@
       </c>
       <c r="J4" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6849,10 +5726,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="9"/>
+      <c r="J5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10"/>
@@ -6864,10 +5738,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="13"/>
+      <c r="J6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6"/>
@@ -6879,10 +5750,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="9"/>
+      <c r="J7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10"/>
@@ -6894,10 +5762,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="13"/>
+      <c r="J8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6"/>
@@ -6909,10 +5774,7 @@
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="9"/>
+      <c r="J9" s="9"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10"/>
@@ -6924,10 +5786,7 @@
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="13"/>
+      <c r="J10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6"/>
@@ -6939,10 +5798,7 @@
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="9"/>
+      <c r="J11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10"/>
@@ -6954,10 +5810,7 @@
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="13"/>
+      <c r="J12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6"/>
@@ -6969,10 +5822,7 @@
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="9"/>
+      <c r="J13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10"/>
@@ -6984,10 +5834,7 @@
       <c r="G14" s="12"/>
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="13"/>
+      <c r="J14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6"/>
@@ -6999,10 +5846,7 @@
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="9"/>
+      <c r="J15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10"/>
@@ -7014,10 +5858,7 @@
       <c r="G16" s="12"/>
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="13"/>
+      <c r="J16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6"/>
@@ -7029,10 +5870,7 @@
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="9"/>
+      <c r="J17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10"/>
@@ -7044,10 +5882,7 @@
       <c r="G18" s="12"/>
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="13"/>
+      <c r="J18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6"/>
@@ -7059,35 +5894,27 @@
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="9"/>
+      <c r="J19" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C22" s="21"/>
       <c r="D22" s="21"/>
       <c r="E22" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F22" s="21"/>
       <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
+      <c r="H22" s="22" t="s">
+        <v>42</v>
+      </c>
       <c r="I22" s="21"/>
-      <c r="J22" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="K22" s="21"/>
-      <c r="L22" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="M22" s="21"/>
+      <c r="J22" s="21"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
@@ -7119,15 +5946,6 @@
       </c>
       <c r="J23" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7140,10 +5958,7 @@
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="9"/>
+      <c r="J24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10"/>
@@ -7155,10 +5970,7 @@
       <c r="G25" s="12"/>
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="13"/>
+      <c r="J25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6"/>
@@ -7170,10 +5982,7 @@
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="9"/>
+      <c r="J26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10"/>
@@ -7185,10 +5994,7 @@
       <c r="G27" s="12"/>
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="13"/>
+      <c r="J27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6"/>
@@ -7200,10 +6006,7 @@
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="9"/>
+      <c r="J28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10"/>
@@ -7215,10 +6018,7 @@
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="13"/>
+      <c r="J29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6"/>
@@ -7230,10 +6030,7 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="9"/>
+      <c r="J30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10"/>
@@ -7245,10 +6042,7 @@
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="13"/>
+      <c r="J31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6"/>
@@ -7260,10 +6054,7 @@
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="9"/>
+      <c r="J32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10"/>
@@ -7275,10 +6066,7 @@
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="13"/>
+      <c r="J33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6"/>
@@ -7290,10 +6078,7 @@
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="9"/>
+      <c r="J34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10"/>
@@ -7305,10 +6090,7 @@
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="13"/>
+      <c r="J35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6"/>
@@ -7320,10 +6102,7 @@
       <c r="G36" s="8"/>
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="9"/>
+      <c r="J36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10"/>
@@ -7335,10 +6114,7 @@
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
       <c r="I37" s="12"/>
-      <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="13"/>
+      <c r="J37" s="13"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6"/>
@@ -7350,35 +6126,27 @@
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="9"/>
+      <c r="J38" s="9"/>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C41" s="21"/>
       <c r="D41" s="21"/>
       <c r="E41" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F41" s="21"/>
       <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
+      <c r="H41" s="22" t="s">
+        <v>42</v>
+      </c>
       <c r="I41" s="21"/>
-      <c r="J41" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="K41" s="21"/>
-      <c r="L41" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="M41" s="21"/>
+      <c r="J41" s="21"/>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
@@ -7410,15 +6178,6 @@
       </c>
       <c r="J42" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="K42" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L42" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7431,10 +6190,7 @@
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="7"/>
-      <c r="M43" s="9"/>
+      <c r="J43" s="9"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10"/>
@@ -7446,10 +6202,7 @@
       <c r="G44" s="12"/>
       <c r="H44" s="12"/>
       <c r="I44" s="12"/>
-      <c r="J44" s="12"/>
-      <c r="K44" s="12"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="13"/>
+      <c r="J44" s="13"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6"/>
@@ -7461,10 +6214,7 @@
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
-      <c r="L45" s="7"/>
-      <c r="M45" s="9"/>
+      <c r="J45" s="9"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10"/>
@@ -7476,10 +6226,7 @@
       <c r="G46" s="12"/>
       <c r="H46" s="12"/>
       <c r="I46" s="12"/>
-      <c r="J46" s="12"/>
-      <c r="K46" s="12"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="13"/>
+      <c r="J46" s="13"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6"/>
@@ -7491,10 +6238,7 @@
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="7"/>
-      <c r="M47" s="9"/>
+      <c r="J47" s="9"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10"/>
@@ -7506,10 +6250,7 @@
       <c r="G48" s="12"/>
       <c r="H48" s="12"/>
       <c r="I48" s="12"/>
-      <c r="J48" s="12"/>
-      <c r="K48" s="12"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="13"/>
+      <c r="J48" s="13"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6"/>
@@ -7521,10 +6262,7 @@
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
-      <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
-      <c r="L49" s="7"/>
-      <c r="M49" s="9"/>
+      <c r="J49" s="9"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10"/>
@@ -7536,10 +6274,7 @@
       <c r="G50" s="12"/>
       <c r="H50" s="12"/>
       <c r="I50" s="12"/>
-      <c r="J50" s="12"/>
-      <c r="K50" s="12"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="13"/>
+      <c r="J50" s="13"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6"/>
@@ -7551,10 +6286,7 @@
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="9"/>
+      <c r="J51" s="9"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10"/>
@@ -7566,10 +6298,7 @@
       <c r="G52" s="12"/>
       <c r="H52" s="12"/>
       <c r="I52" s="12"/>
-      <c r="J52" s="12"/>
-      <c r="K52" s="12"/>
-      <c r="L52" s="11"/>
-      <c r="M52" s="13"/>
+      <c r="J52" s="13"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6"/>
@@ -7581,10 +6310,7 @@
       <c r="G53" s="8"/>
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
-      <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
-      <c r="L53" s="7"/>
-      <c r="M53" s="9"/>
+      <c r="J53" s="9"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10"/>
@@ -7596,10 +6322,7 @@
       <c r="G54" s="12"/>
       <c r="H54" s="12"/>
       <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
-      <c r="K54" s="12"/>
-      <c r="L54" s="11"/>
-      <c r="M54" s="13"/>
+      <c r="J54" s="13"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6"/>
@@ -7611,10 +6334,7 @@
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
-      <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
-      <c r="L55" s="7"/>
-      <c r="M55" s="9"/>
+      <c r="J55" s="9"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10"/>
@@ -7626,10 +6346,7 @@
       <c r="G56" s="12"/>
       <c r="H56" s="12"/>
       <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
-      <c r="K56" s="12"/>
-      <c r="L56" s="11"/>
-      <c r="M56" s="13"/>
+      <c r="J56" s="13"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6"/>
@@ -7641,35 +6358,27 @@
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
-      <c r="J57" s="8"/>
-      <c r="K57" s="8"/>
-      <c r="L57" s="7"/>
-      <c r="M57" s="9"/>
+      <c r="J57" s="9"/>
     </row>
     <row r="60" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="19" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
       <c r="E60" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F60" s="21"/>
       <c r="G60" s="21"/>
-      <c r="H60" s="21"/>
+      <c r="H60" s="22" t="s">
+        <v>42</v>
+      </c>
       <c r="I60" s="21"/>
-      <c r="J60" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="K60" s="21"/>
-      <c r="L60" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="M60" s="21"/>
+      <c r="J60" s="21"/>
     </row>
     <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
@@ -7701,15 +6410,6 @@
       </c>
       <c r="J61" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="K61" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L61" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M61" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7722,10 +6422,7 @@
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
-      <c r="J62" s="8"/>
-      <c r="K62" s="8"/>
-      <c r="L62" s="7"/>
-      <c r="M62" s="9"/>
+      <c r="J62" s="9"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10"/>
@@ -7737,10 +6434,7 @@
       <c r="G63" s="12"/>
       <c r="H63" s="12"/>
       <c r="I63" s="12"/>
-      <c r="J63" s="12"/>
-      <c r="K63" s="12"/>
-      <c r="L63" s="11"/>
-      <c r="M63" s="13"/>
+      <c r="J63" s="13"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6"/>
@@ -7752,10 +6446,7 @@
       <c r="G64" s="8"/>
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
-      <c r="J64" s="8"/>
-      <c r="K64" s="8"/>
-      <c r="L64" s="7"/>
-      <c r="M64" s="9"/>
+      <c r="J64" s="9"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10"/>
@@ -7767,10 +6458,7 @@
       <c r="G65" s="12"/>
       <c r="H65" s="12"/>
       <c r="I65" s="12"/>
-      <c r="J65" s="12"/>
-      <c r="K65" s="12"/>
-      <c r="L65" s="11"/>
-      <c r="M65" s="13"/>
+      <c r="J65" s="13"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6"/>
@@ -7782,10 +6470,7 @@
       <c r="G66" s="8"/>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
-      <c r="J66" s="8"/>
-      <c r="K66" s="8"/>
-      <c r="L66" s="7"/>
-      <c r="M66" s="9"/>
+      <c r="J66" s="9"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10"/>
@@ -7797,10 +6482,7 @@
       <c r="G67" s="12"/>
       <c r="H67" s="12"/>
       <c r="I67" s="12"/>
-      <c r="J67" s="12"/>
-      <c r="K67" s="12"/>
-      <c r="L67" s="11"/>
-      <c r="M67" s="13"/>
+      <c r="J67" s="13"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6"/>
@@ -7812,10 +6494,7 @@
       <c r="G68" s="8"/>
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
-      <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="7"/>
-      <c r="M68" s="9"/>
+      <c r="J68" s="9"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10"/>
@@ -7827,10 +6506,7 @@
       <c r="G69" s="12"/>
       <c r="H69" s="12"/>
       <c r="I69" s="12"/>
-      <c r="J69" s="12"/>
-      <c r="K69" s="12"/>
-      <c r="L69" s="11"/>
-      <c r="M69" s="13"/>
+      <c r="J69" s="13"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6"/>
@@ -7842,10 +6518,7 @@
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
-      <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="7"/>
-      <c r="M70" s="9"/>
+      <c r="J70" s="9"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10"/>
@@ -7857,10 +6530,7 @@
       <c r="G71" s="12"/>
       <c r="H71" s="12"/>
       <c r="I71" s="12"/>
-      <c r="J71" s="12"/>
-      <c r="K71" s="12"/>
-      <c r="L71" s="11"/>
-      <c r="M71" s="13"/>
+      <c r="J71" s="13"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6"/>
@@ -7872,10 +6542,7 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
-      <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="7"/>
-      <c r="M72" s="9"/>
+      <c r="J72" s="9"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10"/>
@@ -7887,10 +6554,7 @@
       <c r="G73" s="12"/>
       <c r="H73" s="12"/>
       <c r="I73" s="12"/>
-      <c r="J73" s="12"/>
-      <c r="K73" s="12"/>
-      <c r="L73" s="11"/>
-      <c r="M73" s="13"/>
+      <c r="J73" s="13"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6"/>
@@ -7902,10 +6566,7 @@
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="7"/>
-      <c r="M74" s="9"/>
+      <c r="J74" s="9"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="10"/>
@@ -7917,10 +6578,7 @@
       <c r="G75" s="12"/>
       <c r="H75" s="12"/>
       <c r="I75" s="12"/>
-      <c r="J75" s="12"/>
-      <c r="K75" s="12"/>
-      <c r="L75" s="11"/>
-      <c r="M75" s="13"/>
+      <c r="J75" s="13"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6"/>
@@ -7932,22 +6590,19 @@
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
       <c r="I76" s="8"/>
-      <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="7"/>
-      <c r="M76" s="9"/>
+      <c r="J76" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="F3:G3"/>
     <mergeCell ref="C22:D22"/>
-    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="F22:G22"/>
     <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="F41:G41"/>
     <mergeCell ref="C60:D60"/>
-    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="F60:G60"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:A19">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -8005,8 +6660,8 @@
       <formula>OR($A62="Accesorios",$A62="Vuelta a la calma")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="20">
-    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K3 M3 K22 M22 K41 M41 K60 M60" type="decimal">
+  <dataValidations count="15">
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I3:J3 I22:J22 I41:J41 I60:J60" type="decimal">
       <formula1>0</formula1>
       <formula2>10</formula2>
     </dataValidation>
@@ -8034,10 +6689,6 @@
       <formula1>"Sí"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Minutos del aeróbico (0,5 = 30 s)." errorStyle="stop" errorTitle="Minutos" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J5:J19 J24:J38 J43:J57 J62:J76" type="decimal">
-      <formula1>0</formula1>
-      <formula2>600</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C3" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -8046,10 +6697,6 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K5:K19" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C22" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -8058,10 +6705,6 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K24:K38" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C41" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -8070,20 +6713,12 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K43:K57" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C60" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Elige un bloque del desplegable." errorStyle="stop" errorTitle="Bloque" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A62:A76" type="list">
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K62:K76" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
